--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -8,6 +8,7 @@
   <x:sheets>
     <x:sheet name="March 2025" sheetId="7" r:id="rId7"/>
     <x:sheet name="January 2026" sheetId="8" r:id="rId8"/>
+    <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -128,6 +129,18 @@
   </x:si>
   <x:si>
     <x:t>61-1-2026-1021-486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENE CLOMA NAPULI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok 6, Lumbocan, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLM-21-6196-XIII</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1050-991</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3355,4 +3368,1255 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="2" t="s"/>
+      <x:c r="B3" s="2">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s"/>
+      <x:c r="D3" s="2" t="s"/>
+      <x:c r="E3" s="2" t="s"/>
+      <x:c r="F3" s="2" t="s"/>
+      <x:c r="G3" s="2" t="s"/>
+      <x:c r="H3" s="2" t="s"/>
+      <x:c r="I3" s="2" t="s"/>
+      <x:c r="J3" s="2" t="s"/>
+      <x:c r="K3" s="2" t="s"/>
+      <x:c r="L3" s="2" t="s"/>
+      <x:c r="M3" s="2" t="s"/>
+      <x:c r="N3" s="2" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="2" t="s"/>
+      <x:c r="B4" s="2" t="s"/>
+      <x:c r="C4" s="2" t="s"/>
+      <x:c r="D4" s="2" t="s"/>
+      <x:c r="E4" s="2" t="s"/>
+      <x:c r="F4" s="2" t="s"/>
+      <x:c r="G4" s="2" t="s"/>
+      <x:c r="H4" s="2" t="s"/>
+      <x:c r="I4" s="2" t="s"/>
+      <x:c r="J4" s="2" t="s"/>
+      <x:c r="K4" s="2" t="s"/>
+      <x:c r="L4" s="2" t="s"/>
+      <x:c r="M4" s="2" t="s"/>
+      <x:c r="N4" s="2" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A5" s="3" t="s"/>
+      <x:c r="B5" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="s"/>
+      <x:c r="O5" s="6" t="s"/>
+      <x:c r="P5" s="6" t="s"/>
+      <x:c r="Q5" s="6" t="s"/>
+      <x:c r="R5" s="6" t="s"/>
+      <x:c r="S5" s="6" t="s"/>
+      <x:c r="T5" s="6" t="s"/>
+      <x:c r="U5" s="6" t="s"/>
+      <x:c r="V5" s="6" t="s"/>
+      <x:c r="W5" s="6" t="s"/>
+      <x:c r="X5" s="6" t="s"/>
+      <x:c r="Y5" s="6" t="s"/>
+      <x:c r="Z5" s="6" t="s"/>
+      <x:c r="AA5" s="6" t="s"/>
+      <x:c r="AB5" s="6" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A6" s="7" t="s"/>
+      <x:c r="B6" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H6" s="12">
+        <x:v>46093.1010416667</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>1516186</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L6" s="12">
+        <x:v>46093.1172800926</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="s"/>
+      <x:c r="O6" s="9" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="B7" s="8" t="s"/>
+      <x:c r="C7" s="8" t="s"/>
+      <x:c r="D7" s="8" t="s"/>
+      <x:c r="E7" s="8" t="s"/>
+      <x:c r="F7" s="8" t="s"/>
+      <x:c r="G7" s="8" t="s"/>
+      <x:c r="H7" s="8" t="s"/>
+      <x:c r="I7" s="8" t="s"/>
+      <x:c r="J7" s="8" t="s"/>
+      <x:c r="K7" s="8" t="s"/>
+      <x:c r="L7" s="8" t="s"/>
+      <x:c r="M7" s="8" t="s"/>
+      <x:c r="N7" s="7" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="s"/>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="17" t="s"/>
+      <x:c r="F9" s="17" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="s"/>
+      <x:c r="D10" s="19" t="s"/>
+      <x:c r="E10" s="19" t="s"/>
+      <x:c r="F10" s="20" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B12" s="24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="6">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B9:F9"/>
+    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B12:E12"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -11,58 +11,22 @@
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
@@ -150,7 +114,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -177,12 +141,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -193,17 +151,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -211,7 +175,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -223,9 +187,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -252,15 +225,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -272,14 +245,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -297,10 +270,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -311,13 +284,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -460,8 +450,42 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thick">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -472,40 +496,40 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -514,16 +538,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -532,71 +553,97 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -608,20 +655,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -629,6 +676,34 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -892,190 +967,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45717</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45743.3040046296</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="14">
         <x:v>45537</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>45743.3122337963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s"/>
+      <x:c r="C7" s="17" t="s"/>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s"/>
+      <x:c r="F7" s="17" t="s"/>
+      <x:c r="G7" s="17" t="s"/>
+      <x:c r="H7" s="17" t="s"/>
+      <x:c r="I7" s="17" t="s"/>
+      <x:c r="J7" s="17" t="s"/>
+      <x:c r="K7" s="17" t="s"/>
+      <x:c r="L7" s="17" t="s"/>
+      <x:c r="M7" s="17" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
+      <x:c r="B9" s="18" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s"/>
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="s"/>
+      <x:c r="D10" s="22" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
+      <x:c r="B11" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="25" t="s"/>
+      <x:c r="F11" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
+      <x:c r="B12" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2143,226 +2214,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46030.2246064815</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46030.2246296296</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>46030.2605555556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
         <x:v>46036.0630902778</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="31">
         <x:v>46036.063125</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="30" t="n">
         <x:v>1478245</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="31">
         <x:v>46036.082037037</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="30" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="B10" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="34" t="s"/>
+      <x:c r="D10" s="34" t="s"/>
+      <x:c r="E10" s="35" t="s"/>
+      <x:c r="F10" s="35" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B11" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="B12" s="24" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3429,190 +3502,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46093.1010416667</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="14">
         <x:v>45374</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1516186</x:v>
       </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="K6" s="15" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="16">
         <x:v>46093.1172800926</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s"/>
+      <x:c r="C7" s="17" t="s"/>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s"/>
+      <x:c r="F7" s="17" t="s"/>
+      <x:c r="G7" s="17" t="s"/>
+      <x:c r="H7" s="17" t="s"/>
+      <x:c r="I7" s="17" t="s"/>
+      <x:c r="J7" s="17" t="s"/>
+      <x:c r="K7" s="17" t="s"/>
+      <x:c r="L7" s="17" t="s"/>
+      <x:c r="M7" s="17" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
+      <x:c r="B9" s="18" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s"/>
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="s"/>
+      <x:c r="D10" s="22" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="23" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
+      <x:c r="B11" s="24" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="s"/>
+      <x:c r="D11" s="25" t="s"/>
+      <x:c r="E11" s="25" t="s"/>
+      <x:c r="F11" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
+      <x:c r="B12" s="27" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="s"/>
+      <x:c r="D12" s="28" t="s"/>
+      <x:c r="E12" s="28" t="s"/>
+      <x:c r="F12" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,9 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAN JOSEPH JAMERO</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
@@ -114,7 +117,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -175,7 +178,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -192,14 +195,6 @@
       <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="18"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -225,7 +220,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="17">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -270,10 +265,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -284,30 +279,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -450,42 +428,8 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thick">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -526,10 +470,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -538,13 +485,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -553,26 +500,14 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -639,11 +574,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -655,11 +594,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -667,8 +602,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -676,10 +615,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -693,18 +628,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -952,7 +875,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -969,7 +894,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45717</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1032,22 +957,22 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45743.3040046296</x:v>
@@ -1065,7 +990,7 @@
         <x:v>45743.3122337963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -1101,1277 +1026,6 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="18" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s"/>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="21" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s"/>
-      <x:c r="D10" s="22" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="23" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="24" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s"/>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
-  </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="0" summaryRight="0"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:AB993"/>
-  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
-    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
-      <x:c r="N5" s="4" t="s"/>
-      <x:c r="O5" s="5" t="s"/>
-      <x:c r="P5" s="5" t="s"/>
-      <x:c r="Q5" s="5" t="s"/>
-      <x:c r="R5" s="5" t="s"/>
-      <x:c r="S5" s="5" t="s"/>
-      <x:c r="T5" s="5" t="s"/>
-      <x:c r="U5" s="5" t="s"/>
-      <x:c r="V5" s="5" t="s"/>
-      <x:c r="W5" s="5" t="s"/>
-      <x:c r="X5" s="5" t="s"/>
-      <x:c r="Y5" s="5" t="s"/>
-      <x:c r="Z5" s="5" t="s"/>
-      <x:c r="AA5" s="5" t="s"/>
-      <x:c r="AB5" s="5" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46030.2246064815</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46030.2246296296</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46030.2605555556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="s"/>
-      <x:c r="O6" s="7" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="30" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="30" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E7" s="30" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="30" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="30" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="31">
-        <x:v>46036.0630902778</x:v>
-      </x:c>
-      <x:c r="I7" s="31">
-        <x:v>46036.063125</x:v>
-      </x:c>
-      <x:c r="J7" s="30" t="n">
-        <x:v>1478245</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="31">
-        <x:v>46036.082037037</x:v>
-      </x:c>
-      <x:c r="M7" s="30" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
-    </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
       <x:c r="C9" s="9" t="s"/>
@@ -2386,40 +1040,30 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="33" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="34" t="s"/>
-      <x:c r="D10" s="34" t="s"/>
-      <x:c r="E10" s="35" t="s"/>
-      <x:c r="F10" s="35" t="s"/>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
-        <x:v>1</x:v>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
       <x:c r="B13" s="24" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="25" t="s"/>
       <x:c r="D13" s="25" t="s"/>
@@ -2430,13 +1074,13 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="27" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C14" s="28" t="s"/>
       <x:c r="D14" s="28" t="s"/>
       <x:c r="E14" s="28" t="s"/>
       <x:c r="F14" s="29" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3420,10 +2064,10 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -3443,7 +2087,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3487,7 +2131,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3567,22 +2213,1313 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46030.2246064815</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46030.2246296296</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46030.2605555556</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C7" s="30" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H7" s="31">
+        <x:v>46036.0630902778</x:v>
+      </x:c>
+      <x:c r="I7" s="31">
+        <x:v>46036.063125</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="n">
+        <x:v>1478245</x:v>
+      </x:c>
+      <x:c r="K7" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L7" s="31">
+        <x:v>46036.082037037</x:v>
+      </x:c>
+      <x:c r="M7" s="30" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="18" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="24" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46093.1010416667</x:v>
@@ -3600,7 +3537,7 @@
         <x:v>46093.1172800926</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -3636,14 +3573,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="18" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s"/>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -3652,41 +3587,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="21" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="s"/>
-      <x:c r="D10" s="22" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="23" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="24" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="25" t="s"/>
-      <x:c r="D11" s="25" t="s"/>
-      <x:c r="E11" s="25" t="s"/>
-      <x:c r="F11" s="26" t="n">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s"/>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="28" t="s"/>
-      <x:c r="F12" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4667,13 +4610,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -507,7 +507,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -543,33 +543,37 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -619,15 +623,15 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -955,7 +959,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -1011,20 +1015,20 @@
       <x:c r="M7" s="17" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="18" t="s"/>
+      <x:c r="C8" s="18" t="s"/>
+      <x:c r="D8" s="18" t="s"/>
+      <x:c r="E8" s="18" t="s"/>
+      <x:c r="F8" s="18" t="s"/>
+      <x:c r="G8" s="18" t="s"/>
+      <x:c r="H8" s="18" t="s"/>
+      <x:c r="I8" s="18" t="s"/>
+      <x:c r="J8" s="18" t="s"/>
+      <x:c r="K8" s="18" t="s"/>
+      <x:c r="L8" s="18" t="s"/>
+      <x:c r="M8" s="18" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -1042,44 +1046,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2211,7 +2215,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -2251,127 +2255,127 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="30" t="s">
+      <x:c r="B7" s="31" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C7" s="30" t="s">
+      <x:c r="C7" s="31" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D7" s="30" t="s">
+      <x:c r="D7" s="31" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E7" s="30" t="s">
+      <x:c r="E7" s="31" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F7" s="30" t="s">
+      <x:c r="F7" s="31" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G7" s="30" t="s">
+      <x:c r="G7" s="31" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H7" s="31">
+      <x:c r="H7" s="32">
         <x:v>46036.0630902778</x:v>
       </x:c>
-      <x:c r="I7" s="31">
+      <x:c r="I7" s="32">
         <x:v>46036.063125</x:v>
       </x:c>
-      <x:c r="J7" s="30" t="n">
+      <x:c r="J7" s="31" t="n">
         <x:v>1478245</x:v>
       </x:c>
-      <x:c r="K7" s="32" t="n">
+      <x:c r="K7" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L7" s="31">
+      <x:c r="L7" s="32">
         <x:v>46036.082037037</x:v>
       </x:c>
-      <x:c r="M7" s="30" t="s">
+      <x:c r="M7" s="31" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="18" t="s"/>
+      <x:c r="C8" s="18" t="s"/>
+      <x:c r="D8" s="18" t="s"/>
+      <x:c r="E8" s="18" t="s"/>
+      <x:c r="F8" s="18" t="s"/>
+      <x:c r="G8" s="18" t="s"/>
+      <x:c r="H8" s="18" t="s"/>
+      <x:c r="I8" s="18" t="s"/>
+      <x:c r="J8" s="18" t="s"/>
+      <x:c r="K8" s="18" t="s"/>
+      <x:c r="L8" s="18" t="s"/>
+      <x:c r="M8" s="18" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="18" t="s"/>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="18" t="s"/>
+      <x:c r="F9" s="18" t="s"/>
+      <x:c r="G9" s="18" t="s"/>
+      <x:c r="H9" s="18" t="s"/>
+      <x:c r="I9" s="18" t="s"/>
+      <x:c r="J9" s="18" t="s"/>
+      <x:c r="K9" s="18" t="s"/>
+      <x:c r="L9" s="18" t="s"/>
+      <x:c r="M9" s="18" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3502,7 +3506,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -3558,20 +3562,20 @@
       <x:c r="M7" s="17" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="18" t="s"/>
+      <x:c r="C8" s="18" t="s"/>
+      <x:c r="D8" s="18" t="s"/>
+      <x:c r="E8" s="18" t="s"/>
+      <x:c r="F8" s="18" t="s"/>
+      <x:c r="G8" s="18" t="s"/>
+      <x:c r="H8" s="18" t="s"/>
+      <x:c r="I8" s="18" t="s"/>
+      <x:c r="J8" s="18" t="s"/>
+      <x:c r="K8" s="18" t="s"/>
+      <x:c r="L8" s="18" t="s"/>
+      <x:c r="M8" s="18" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3589,44 +3593,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="19" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="20" t="s"/>
+      <x:c r="D11" s="20" t="s"/>
+      <x:c r="E11" s="21" t="s"/>
+      <x:c r="F11" s="21" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="23" t="s"/>
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="24" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="25" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="26" t="s"/>
+      <x:c r="D13" s="26" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="29" t="s"/>
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="29" t="s"/>
+      <x:c r="F14" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -929,7 +929,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -999,7 +999,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s"/>
       <x:c r="C7" s="17" t="s"/>
@@ -2185,7 +2185,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2255,7 +2255,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="31" t="s">
         <x:v>19</x:v>
@@ -3476,7 +3476,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3546,7 +3546,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s"/>
       <x:c r="C7" s="17" t="s"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,12 +24,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>JAN JOSEPH JAMERO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
@@ -162,15 +198,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -190,11 +226,10 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
-      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -429,7 +464,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -440,12 +475,18 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -455,15 +496,6 @@
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -485,10 +517,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -500,14 +535,8 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -538,40 +567,24 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -598,15 +611,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -620,18 +633,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -931,18 +932,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -960,75 +949,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45743.3040046296</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45537</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45743.3122337963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s"/>
-      <x:c r="C7" s="17" t="s"/>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s"/>
-      <x:c r="F7" s="17" t="s"/>
-      <x:c r="G7" s="17" t="s"/>
-      <x:c r="H7" s="17" t="s"/>
-      <x:c r="I7" s="17" t="s"/>
-      <x:c r="J7" s="17" t="s"/>
-      <x:c r="K7" s="17" t="s"/>
-      <x:c r="L7" s="17" t="s"/>
-      <x:c r="M7" s="17" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45743.3040046296</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45537</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45743.3122337963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -1046,44 +1047,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="B11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
+      <x:c r="B13" s="21" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2187,18 +2188,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2216,166 +2205,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46030.2246064815</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46030.2246296296</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46030.2605555556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="31" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H7" s="32">
-        <x:v>46036.0630902778</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46036.063125</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="n">
-        <x:v>1478245</x:v>
-      </x:c>
-      <x:c r="K7" s="33" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="32">
-        <x:v>46036.082037037</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46030.2246064815</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46030.2246296296</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46030.2605555556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="18" t="s"/>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="18" t="s"/>
-      <x:c r="F9" s="18" t="s"/>
-      <x:c r="G9" s="18" t="s"/>
-      <x:c r="H9" s="18" t="s"/>
-      <x:c r="I9" s="18" t="s"/>
-      <x:c r="J9" s="18" t="s"/>
-      <x:c r="K9" s="18" t="s"/>
-      <x:c r="L9" s="18" t="s"/>
-      <x:c r="M9" s="18" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46036.0630902778</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46036.063125</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1478245</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46036.082037037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
-        <x:v>11</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3478,18 +3479,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3507,75 +3496,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46093.1010416667</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45374</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1516186</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46093.1172800926</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s"/>
-      <x:c r="C7" s="17" t="s"/>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s"/>
-      <x:c r="F7" s="17" t="s"/>
-      <x:c r="G7" s="17" t="s"/>
-      <x:c r="H7" s="17" t="s"/>
-      <x:c r="I7" s="17" t="s"/>
-      <x:c r="J7" s="17" t="s"/>
-      <x:c r="K7" s="17" t="s"/>
-      <x:c r="L7" s="17" t="s"/>
-      <x:c r="M7" s="17" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="18" t="s"/>
-      <x:c r="C8" s="18" t="s"/>
-      <x:c r="D8" s="18" t="s"/>
-      <x:c r="E8" s="18" t="s"/>
-      <x:c r="F8" s="18" t="s"/>
-      <x:c r="G8" s="18" t="s"/>
-      <x:c r="H8" s="18" t="s"/>
-      <x:c r="I8" s="18" t="s"/>
-      <x:c r="J8" s="18" t="s"/>
-      <x:c r="K8" s="18" t="s"/>
-      <x:c r="L8" s="18" t="s"/>
-      <x:c r="M8" s="18" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46093.1010416667</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1516186</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46093.1172800926</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3593,44 +3594,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="19" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="20" t="s"/>
-      <x:c r="D11" s="20" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="21" t="s"/>
+      <x:c r="B11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s"/>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="17" t="s"/>
+      <x:c r="F11" s="17" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s"/>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="24" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="20" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="25" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="27" t="n">
+      <x:c r="B13" s="21" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="30" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,12 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>JAN JOSEPH JAMERO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIII | March 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -101,6 +104,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIII | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -134,6 +140,9 @@
     <x:t>61-1-2026-1021-486</x:t>
   </x:si>
   <x:si>
+    <x:t>XIII | March 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENE CLOMA NAPULI</x:t>
   </x:si>
   <x:si>
@@ -153,7 +162,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -193,6 +202,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -464,14 +497,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -484,59 +526,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -567,71 +609,83 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -860,58 +914,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -954,81 +1008,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45743.3040046296</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45537</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45743.3122337963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1047,44 +1101,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2071,7 +2125,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -2116,58 +2170,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2210,173 +2264,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46030.2246064815</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46030.2246296296</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46030.2605555556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="F9" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46036.0630902778</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="15">
         <x:v>46036.063125</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1478245</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46036.082037037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3361,7 +3415,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -3407,58 +3461,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3501,81 +3555,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46093.1010416667</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="16">
         <x:v>45374</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1516186</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46093.1172800926</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3594,44 +3648,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4618,7 +4672,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,6 +69,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
@@ -159,10 +195,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -207,15 +245,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -231,15 +261,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -254,13 +284,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -502,21 +525,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -526,59 +549,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -609,83 +632,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -914,78 +945,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1006,7 +1049,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1046,1392 +1089,139 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45743.3040046296</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I10" s="17">
         <x:v>45537</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45743.3122337963</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
-  </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="0" summaryRight="0"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:AB993"/>
-  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
-    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
-      <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28">
-      <x:c r="A5" s="4" t="s"/>
-      <x:c r="N5" s="4" t="s"/>
-      <x:c r="O5" s="5" t="s"/>
-      <x:c r="P5" s="5" t="s"/>
-      <x:c r="Q5" s="5" t="s"/>
-      <x:c r="R5" s="5" t="s"/>
-      <x:c r="S5" s="5" t="s"/>
-      <x:c r="T5" s="5" t="s"/>
-      <x:c r="U5" s="5" t="s"/>
-      <x:c r="V5" s="5" t="s"/>
-      <x:c r="W5" s="5" t="s"/>
-      <x:c r="X5" s="5" t="s"/>
-      <x:c r="Y5" s="5" t="s"/>
-      <x:c r="Z5" s="5" t="s"/>
-      <x:c r="AA5" s="5" t="s"/>
-      <x:c r="AB5" s="5" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="N6" s="6" t="s"/>
-      <x:c r="O6" s="7" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E7" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F7" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="13" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H7" s="13" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I7" s="13" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J7" s="13" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="13" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46030.2246064815</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46030.2246296296</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46030.2605555556</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46036.0630902778</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46036.063125</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1478245</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46036.082037037</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>2</x:v>
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3413,14 +2203,1368 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J7" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46030.2246064815</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46030.2246296296</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46030.2605555556</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46036.0630902778</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46036.063125</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1478245</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46036.082037037</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="9">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3461,78 +3605,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3553,7 +3709,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3593,104 +3749,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46093.1010416667</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I10" s="17">
         <x:v>45374</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1516186</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46093.1172800926</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4669,14 +4862,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,42 +69,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (RENEWAL)</x:t>
@@ -200,7 +164,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -244,14 +208,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -266,10 +222,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -284,6 +248,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -528,16 +499,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -549,24 +520,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -585,10 +553,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -601,7 +572,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -632,28 +603,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -668,10 +631,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -696,15 +655,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1049,7 +1008,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1089,138 +1048,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45743.3040046296</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45537</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45743.3122337963</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45743.3040046296</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45537</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45743.3122337963</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2322,7 +2244,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2355,7 +2277,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2395,187 +2317,137 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46030.2246064815</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46030.2246296296</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>123456</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46030.2605555556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46036.0630902778</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46036.063125</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1478245</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46036.082037037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46030.2246064815</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46030.2246296296</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46030.2605555556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46036.0630902778</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46036.063125</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1478245</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46036.082037037</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="B14" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B15" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="23" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3676,7 +3548,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3709,7 +3581,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3749,138 +3621,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46093.1010416667</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1516186</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46093.1172800926</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46093.1010416667</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45374</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1516186</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46093.1172800926</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -1102,50 +1102,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2129,10 +2129,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2396,61 +2396,61 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3432,11 +3432,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3675,50 +3675,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4702,10 +4702,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -141,6 +141,90 @@
   </x:si>
   <x:si>
     <x:t>XIII | March 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AIKO AMONCION PAGAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok katmon, cayali, Tago, Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07428-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1056-793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAROLD PEQIUNO CODILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok-3, san vicente, Tagbina, Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07421-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1053-570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMAEL ANSAYAM MALAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok- 1 katugasan, comagascas, City Of Cabadbaran, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07433-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1057-943</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEEMARK VILLARINO FLORES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok-6, Kinamlutan, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07426-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1055-802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JERWIN DACAPO WARIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok-7, camagong, Nasipit, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07438-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1059-133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENATO TIEMPO DINGAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok- sunflower, gamut, Tago, Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07435-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1058-206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILLIAM LANGOTE GATELA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>purok - Padigusan, sta, cruz, Rosario, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07423-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1054-261</x:t>
   </x:si>
   <x:si>
     <x:t>RENE CLOMA NAPULI</x:t>
@@ -491,7 +575,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -571,8 +655,14 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -677,6 +767,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3624,13 +3734,13 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>40</x:v>
@@ -3642,89 +3752,345 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46093.1010416667</x:v>
+        <x:v>46100.107974537</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>45374</x:v>
+        <x:v>46100.1417939815</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1516186</x:v>
+        <x:v>1516232</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>450</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46093.1172800926</x:v>
+        <x:v>46100.1612384259</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46100.0888657407</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46100.1424884259</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1516235</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46100.1669907407</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46100.1182175926</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>46100.1415972222</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="n">
+        <x:v>1516229</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46100.1503240741</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
+        <x:v>46100.1012268519</x:v>
+      </x:c>
+      <x:c r="I11" s="31">
+        <x:v>46100.1420138889</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="n">
+        <x:v>1516233</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L11" s="33">
+        <x:v>46100.163287037</x:v>
+      </x:c>
+      <x:c r="M11" s="29" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H12" s="31">
+        <x:v>46100.1284375</x:v>
+      </x:c>
+      <x:c r="I12" s="31">
+        <x:v>46100.1411111111</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="n">
+        <x:v>1516231</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="33">
+        <x:v>46100.1586689815</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H13" s="31">
+        <x:v>46100.1227893519</x:v>
+      </x:c>
+      <x:c r="I13" s="31">
+        <x:v>46100.1413888889</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="n">
+        <x:v>1516230</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L13" s="33">
+        <x:v>46100.1550810185</x:v>
+      </x:c>
+      <x:c r="M13" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D14" s="30" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E14" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F14" s="29" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G14" s="29" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H14" s="31">
+        <x:v>46100.0935300926</x:v>
+      </x:c>
+      <x:c r="I14" s="31">
+        <x:v>46100.1422800926</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="n">
+        <x:v>1516234</x:v>
+      </x:c>
+      <x:c r="K14" s="32" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="33">
+        <x:v>46100.165162037</x:v>
+      </x:c>
+      <x:c r="M14" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
-        <x:v>1</x:v>
+      <x:c r="C15" s="29" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="29" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F15" s="29" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G15" s="29" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H15" s="31">
+        <x:v>46093.1010416667</x:v>
+      </x:c>
+      <x:c r="I15" s="31">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J15" s="30" t="n">
+        <x:v>1516186</x:v>
+      </x:c>
+      <x:c r="K15" s="32" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L15" s="33">
+        <x:v>46093.1172800926</x:v>
+      </x:c>
+      <x:c r="M15" s="29" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="s"/>
+      <x:c r="D18" s="18" t="s"/>
+      <x:c r="E18" s="19" t="s"/>
+      <x:c r="F18" s="19" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="22" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="23" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4697,15 +5063,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -89,6 +89,9 @@
     <x:t>61-3-2025-1131</x:t>
   </x:si>
   <x:si>
+    <x:t>123456</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cherry Mae Anub</x:t>
   </x:si>
   <x:si>
@@ -140,6 +143,9 @@
     <x:t>61-1-2026-1021-486</x:t>
   </x:si>
   <x:si>
+    <x:t>1478245</x:t>
+  </x:si>
+  <x:si>
     <x:t>XIII | March 2026</x:t>
   </x:si>
   <x:si>
@@ -155,6 +161,9 @@
     <x:t>70-3-2026-1056-793</x:t>
   </x:si>
   <x:si>
+    <x:t>1516232</x:t>
+  </x:si>
+  <x:si>
     <x:t>HAROLD PEQIUNO CODILLA</x:t>
   </x:si>
   <x:si>
@@ -167,6 +176,9 @@
     <x:t>70-3-2026-1053-570</x:t>
   </x:si>
   <x:si>
+    <x:t>1516235</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISMAEL ANSAYAM MALAG</x:t>
   </x:si>
   <x:si>
@@ -179,6 +191,9 @@
     <x:t>70-3-2026-1057-943</x:t>
   </x:si>
   <x:si>
+    <x:t>1516229</x:t>
+  </x:si>
+  <x:si>
     <x:t>JEEMARK VILLARINO FLORES</x:t>
   </x:si>
   <x:si>
@@ -191,6 +206,9 @@
     <x:t>70-3-2026-1055-802</x:t>
   </x:si>
   <x:si>
+    <x:t>1516233</x:t>
+  </x:si>
+  <x:si>
     <x:t>JERWIN DACAPO WARIS</x:t>
   </x:si>
   <x:si>
@@ -203,6 +221,9 @@
     <x:t>70-3-2026-1059-133</x:t>
   </x:si>
   <x:si>
+    <x:t>1516231</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENATO TIEMPO DINGAL</x:t>
   </x:si>
   <x:si>
@@ -215,6 +236,9 @@
     <x:t>70-3-2026-1058-206</x:t>
   </x:si>
   <x:si>
+    <x:t>1516230</x:t>
+  </x:si>
+  <x:si>
     <x:t>WILLIAM LANGOTE GATELA</x:t>
   </x:si>
   <x:si>
@@ -227,6 +251,9 @@
     <x:t>70-3-2026-1054-261</x:t>
   </x:si>
   <x:si>
+    <x:t>1516234</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENE CLOMA NAPULI</x:t>
   </x:si>
   <x:si>
@@ -237,6 +264,9 @@
   </x:si>
   <x:si>
     <x:t>70-3-2026-1050-991</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516186</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1179,22 +1209,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45743.3040046296</x:v>
+        <x:v>45743.3040092824</x:v>
       </x:c>
       <x:c r="I8" s="15">
         <x:v>45537</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>123456</x:v>
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45743.3122337963</x:v>
+        <x:v>45743.3122342361</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1214,7 +1244,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -1223,13 +1253,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
@@ -1245,7 +1275,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>
@@ -2354,7 +2384,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2429,86 +2459,86 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46030.2246064815</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46030.2246296296</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>123456</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="G8" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46030.2246127662</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46030.2246403009</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46030.2605555556</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>46030.2605660764</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="D9" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46036.0630902778</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46036.063125</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1478245</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="G9" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46036.0630976157</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
+        <x:v>46036.0631306944</x:v>
+      </x:c>
+      <x:c r="J9" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46036.082037037</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>46036.0820433218</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="18" t="s"/>
       <x:c r="D12" s="18" t="s"/>
@@ -2517,18 +2547,18 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
       <x:c r="B13" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="21" t="s"/>
       <x:c r="D13" s="21" t="s"/>
       <x:c r="E13" s="21" t="s"/>
       <x:c r="F13" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
       <x:c r="B14" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="24" t="s"/>
       <x:c r="D14" s="24" t="s"/>
@@ -2539,7 +2569,7 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="23" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="24" t="s"/>
       <x:c r="D15" s="24" t="s"/>
@@ -2550,7 +2580,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
@@ -3658,7 +3688,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3733,269 +3763,269 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D8" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E8" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46100.107974537</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46100.1417939815</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1516232</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="F8" s="29" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46100.1079781713</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46100.1417990741</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46100.1612384259</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L8" s="33">
+        <x:v>46100.1612414352</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="B9" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46100.0888657407</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46100.1424884259</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1516235</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="D9" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46100.0888710764</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
+        <x:v>46100.1424897801</x:v>
+      </x:c>
+      <x:c r="J9" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46100.1669907407</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="L9" s="33">
+        <x:v>46100.1669975463</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46100.1182175926</x:v>
+        <x:v>46100.1182232523</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46100.1415972222</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1516229</x:v>
+        <x:v>46100.1416081713</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46100.1503240741</x:v>
+        <x:v>46100.1503302546</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46100.1012268519</x:v>
+        <x:v>46100.1012338657</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46100.1420138889</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1516233</x:v>
+        <x:v>46100.1420214352</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="s">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46100.163287037</x:v>
+        <x:v>46100.1632961806</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46100.1284375</x:v>
+        <x:v>46100.1284434491</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46100.1411111111</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1516231</x:v>
+        <x:v>46100.1411114583</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46100.1586689815</x:v>
+        <x:v>46100.1586730671</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46100.1227893519</x:v>
+        <x:v>46100.1227937384</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46100.1413888889</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1516230</x:v>
+        <x:v>46100.1413909606</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46100.1550810185</x:v>
+        <x:v>46100.1550834606</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="29" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46100.0935300926</x:v>
+        <x:v>46100.0935301273</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46100.1422800926</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1516234</x:v>
+        <x:v>46100.1422867824</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46100.165162037</x:v>
+        <x:v>46100.1651693866</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -4003,44 +4033,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>69</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46093.1010416667</x:v>
+        <x:v>46093.1010420255</x:v>
       </x:c>
       <x:c r="I15" s="31">
         <x:v>45374</x:v>
       </x:c>
-      <x:c r="J15" s="30" t="n">
-        <x:v>1516186</x:v>
+      <x:c r="J15" s="30" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46093.1172800926</x:v>
+        <x:v>46093.1172837847</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="18" t="s"/>
       <x:c r="D18" s="18" t="s"/>
@@ -4049,18 +4079,18 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
       <x:c r="B19" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="21" t="s"/>
       <x:c r="D19" s="21" t="s"/>
       <x:c r="E19" s="21" t="s"/>
       <x:c r="F19" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="23" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="24" t="s"/>
       <x:c r="D20" s="24" t="s"/>
@@ -4082,7 +4112,7 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -1148,7 +1148,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1188,7 +1188,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2417,7 +2417,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2457,7 +2457,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>28</x:v>
@@ -2496,7 +2496,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3721,7 +3721,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3761,7 +3761,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>34</x:v>
@@ -3800,7 +3800,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3838,7 +3838,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3876,7 +3876,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3914,7 +3914,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3952,7 +3952,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -3990,7 +3990,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4028,7 +4028,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -147,6 +147,24 @@
   </x:si>
   <x:si>
     <x:t>XIII | March 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATV Station License (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIL PRODUCTS SERVICE TV BUTUAN INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3RD ST.,ALVIOLA VILLAGE, BAAN, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-07864-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1060-843</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516283</x:t>
   </x:si>
   <x:si>
     <x:t>AIKO AMONCION PAGAR</x:t>
@@ -3764,37 +3782,37 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" s="29" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D8" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F8" s="29" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G8" s="29" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H8" s="31">
-        <x:v>46100.1079781713</x:v>
+        <x:v>46111.1470208796</x:v>
       </x:c>
       <x:c r="I8" s="31">
-        <x:v>46100.1417990741</x:v>
+        <x:v>46111.1470245139</x:v>
       </x:c>
       <x:c r="J8" s="30" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K8" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>97720</x:v>
       </x:c>
       <x:c r="L8" s="33">
-        <x:v>46100.1612414352</x:v>
+        <x:v>46111.1717733681</x:v>
       </x:c>
       <x:c r="M8" s="29" t="s">
         <x:v>22</x:v>
@@ -3805,34 +3823,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D9" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E9" s="29" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F9" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G9" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46100.0888710764</x:v>
+        <x:v>46100.1079781713</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46100.1424897801</x:v>
+        <x:v>46100.1417990741</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46100.1669975463</x:v>
+        <x:v>46100.1612414352</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>22</x:v>
@@ -3843,34 +3861,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46100.1182232523</x:v>
+        <x:v>46100.0888710764</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46100.1416081713</x:v>
+        <x:v>46100.1424897801</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46100.1503302546</x:v>
+        <x:v>46100.1669975463</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>22</x:v>
@@ -3881,34 +3899,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46100.1012338657</x:v>
+        <x:v>46100.1182232523</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46100.1420214352</x:v>
+        <x:v>46100.1416081713</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46100.1632961806</x:v>
+        <x:v>46100.1503302546</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>22</x:v>
@@ -3919,34 +3937,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46100.1284434491</x:v>
+        <x:v>46100.1012338657</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46100.1411114583</x:v>
+        <x:v>46100.1420214352</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46100.1586730671</x:v>
+        <x:v>46100.1632961806</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>22</x:v>
@@ -3957,34 +3975,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46100.1227937384</x:v>
+        <x:v>46100.1284434491</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46100.1413909606</x:v>
+        <x:v>46100.1411114583</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46100.1550834606</x:v>
+        <x:v>46100.1586730671</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>22</x:v>
@@ -3995,34 +4013,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46100.0935301273</x:v>
+        <x:v>46100.1227937384</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46100.1422867824</x:v>
+        <x:v>46100.1413909606</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46100.1651693866</x:v>
+        <x:v>46100.1550834606</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>22</x:v>
@@ -4030,78 +4048,105 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46093.1010420255</x:v>
+        <x:v>46100.0935301273</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>45374</x:v>
+        <x:v>46100.1422867824</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
-        <x:v>450</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46093.1172837847</x:v>
+        <x:v>46100.1651693866</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D16" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F16" s="29" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G16" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H16" s="31">
+        <x:v>46093.1010420255</x:v>
+      </x:c>
+      <x:c r="I16" s="31">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J16" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K16" s="32" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L16" s="33">
+        <x:v>46093.1172837847</x:v>
+      </x:c>
+      <x:c r="M16" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C18" s="18" t="s"/>
-      <x:c r="D18" s="18" t="s"/>
-      <x:c r="E18" s="19" t="s"/>
-      <x:c r="F18" s="19" t="s"/>
+      <x:c r="C19" s="18" t="s"/>
+      <x:c r="D19" s="18" t="s"/>
+      <x:c r="E19" s="19" t="s"/>
+      <x:c r="F19" s="19" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="21" t="s"/>
-      <x:c r="F19" s="22" t="s">
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="22" t="s">
         <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C21" s="24" t="s"/>
       <x:c r="D21" s="24" t="s"/>
@@ -4110,19 +4155,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C23" s="24" t="s"/>
+      <x:c r="D23" s="24" t="s"/>
+      <x:c r="E23" s="24" t="s"/>
+      <x:c r="F23" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>8</x:v>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5093,16 +5158,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,9 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
-  <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+  <x:si>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>JAN JOSEPH JAMERO</x:t>
@@ -165,6 +165,24 @@
   </x:si>
   <x:si>
     <x:t>1516283</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LGU MARIHATAG, SURIGAO DEL SUR (MDRRMO)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Marihatag, Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RPTR-MM-00103-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1076-912</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516284</x:t>
   </x:si>
   <x:si>
     <x:t>AIKO AMONCION PAGAR</x:t>
@@ -3820,37 +3838,37 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="29" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="29" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F9" s="29" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G9" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H9" s="31">
-        <x:v>46100.1079781713</x:v>
+        <x:v>46111.3583193056</x:v>
       </x:c>
       <x:c r="I9" s="31">
-        <x:v>46100.1417990741</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J9" s="30" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L9" s="33">
-        <x:v>46100.1612414352</x:v>
+        <x:v>46111.3723021991</x:v>
       </x:c>
       <x:c r="M9" s="29" t="s">
         <x:v>22</x:v>
@@ -3861,34 +3879,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D10" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H10" s="31">
-        <x:v>46100.0888710764</x:v>
+        <x:v>46100.1079781713</x:v>
       </x:c>
       <x:c r="I10" s="31">
-        <x:v>46100.1424897801</x:v>
+        <x:v>46100.1417990741</x:v>
       </x:c>
       <x:c r="J10" s="30" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L10" s="33">
-        <x:v>46100.1669975463</x:v>
+        <x:v>46100.1612414352</x:v>
       </x:c>
       <x:c r="M10" s="29" t="s">
         <x:v>22</x:v>
@@ -3899,34 +3917,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="29" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D11" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="29" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="29" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46100.1182232523</x:v>
+        <x:v>46100.0888710764</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46100.1416081713</x:v>
+        <x:v>46100.1424897801</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46100.1503302546</x:v>
+        <x:v>46100.1669975463</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>22</x:v>
@@ -3937,34 +3955,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D12" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46100.1012338657</x:v>
+        <x:v>46100.1182232523</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46100.1420214352</x:v>
+        <x:v>46100.1416081713</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46100.1632961806</x:v>
+        <x:v>46100.1503302546</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>22</x:v>
@@ -3975,34 +3993,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="29" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D13" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="29" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G13" s="29" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46100.1284434491</x:v>
+        <x:v>46100.1012338657</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46100.1411114583</x:v>
+        <x:v>46100.1420214352</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46100.1586730671</x:v>
+        <x:v>46100.1632961806</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>22</x:v>
@@ -4013,34 +4031,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D14" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46100.1227937384</x:v>
+        <x:v>46100.1284434491</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46100.1413909606</x:v>
+        <x:v>46100.1411114583</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K14" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46100.1550834606</x:v>
+        <x:v>46100.1586730671</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>22</x:v>
@@ -4051,34 +4069,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D15" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F15" s="29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G15" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46100.0935301273</x:v>
+        <x:v>46100.1227937384</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46100.1422867824</x:v>
+        <x:v>46100.1413909606</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46100.1651693866</x:v>
+        <x:v>46100.1550834606</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>22</x:v>
@@ -4086,89 +4104,116 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D16" s="30" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E16" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F16" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G16" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46093.1010420255</x:v>
+        <x:v>46100.0935301273</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>45374</x:v>
+        <x:v>46100.1422867824</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
-        <x:v>450</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46093.1172837847</x:v>
+        <x:v>46100.1651693866</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D17" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="29" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H17" s="31">
+        <x:v>46093.1010420255</x:v>
+      </x:c>
+      <x:c r="I17" s="31">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J17" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K17" s="32" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L17" s="33">
+        <x:v>46093.1172837847</x:v>
+      </x:c>
+      <x:c r="M17" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="17" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C19" s="18" t="s"/>
-      <x:c r="D19" s="18" t="s"/>
-      <x:c r="E19" s="19" t="s"/>
-      <x:c r="F19" s="19" t="s"/>
+      <x:c r="C20" s="18" t="s"/>
+      <x:c r="D20" s="18" t="s"/>
+      <x:c r="E20" s="19" t="s"/>
+      <x:c r="F20" s="19" t="s"/>
     </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="20" t="s">
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="21" t="s"/>
-      <x:c r="F20" s="22" t="s">
+      <x:c r="C21" s="21" t="s"/>
+      <x:c r="D21" s="21" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="22" t="s">
         <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="23" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="24" t="s"/>
       <x:c r="D22" s="24" t="s"/>
       <x:c r="E22" s="24" t="s"/>
       <x:c r="F22" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="24" t="s"/>
       <x:c r="D23" s="24" t="s"/>
@@ -4177,19 +4222,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="25" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C25" s="24" t="s"/>
+      <x:c r="D25" s="24" t="s"/>
+      <x:c r="E25" s="24" t="s"/>
+      <x:c r="F25" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
-        <x:v>9</x:v>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5158,17 +5223,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -258,6 +258,21 @@
   </x:si>
   <x:si>
     <x:t>1516231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIM ERRO MAGUINDA AMPARO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4, San Francisco, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-07928-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-3-2026-1078-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516297</x:t>
   </x:si>
   <x:si>
     <x:t>RENATO TIEMPO DINGAL</x:t>
@@ -4084,19 +4099,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46100.1227937384</x:v>
+        <x:v>46112.1495942824</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46100.1413909606</x:v>
+        <x:v>46112.1682116435</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46100.1550834606</x:v>
+        <x:v>46112.2080237037</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>22</x:v>
@@ -4122,10 +4137,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46100.0935301273</x:v>
+        <x:v>46100.1227937384</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46100.1422867824</x:v>
+        <x:v>46100.1413909606</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>87</x:v>
@@ -4134,7 +4149,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46100.1651693866</x:v>
+        <x:v>46100.1550834606</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>22</x:v>
@@ -4142,13 +4157,13 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="D17" s="30" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E17" s="29" t="s">
         <x:v>89</x:v>
@@ -4160,60 +4175,87 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46093.1010420255</x:v>
+        <x:v>46100.0935301273</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>45374</x:v>
+        <x:v>46100.1422867824</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>450</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46093.1172837847</x:v>
+        <x:v>46100.1651693866</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D18" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="29" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F18" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H18" s="31">
+        <x:v>46093.1010420255</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K18" s="32" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L18" s="33">
+        <x:v>46093.1172837847</x:v>
+      </x:c>
+      <x:c r="M18" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="17" t="s">
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C20" s="18" t="s"/>
-      <x:c r="D20" s="18" t="s"/>
-      <x:c r="E20" s="19" t="s"/>
-      <x:c r="F20" s="19" t="s"/>
+      <x:c r="C21" s="18" t="s"/>
+      <x:c r="D21" s="18" t="s"/>
+      <x:c r="E21" s="19" t="s"/>
+      <x:c r="F21" s="19" t="s"/>
     </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="20" t="s">
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="s"/>
-      <x:c r="D21" s="21" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="22" t="s">
+      <x:c r="C22" s="21" t="s"/>
+      <x:c r="D22" s="21" t="s"/>
+      <x:c r="E22" s="21" t="s"/>
+      <x:c r="F22" s="22" t="s">
         <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="23" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="24" t="s"/>
       <x:c r="D23" s="24" t="s"/>
@@ -4224,38 +4266,48 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="23" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="24" t="s"/>
       <x:c r="D24" s="24" t="s"/>
       <x:c r="E24" s="24" t="s"/>
       <x:c r="F24" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="24" t="s"/>
       <x:c r="D25" s="24" t="s"/>
       <x:c r="E25" s="24" t="s"/>
       <x:c r="F25" s="25" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>10</x:v>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5228,13 +5280,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="March 2025" sheetId="7" r:id="rId7"/>
     <x:sheet name="January 2026" sheetId="8" r:id="rId8"/>
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
+    <x:sheet name="April 2026" sheetId="10" r:id="rId10"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -32,9 +33,6 @@
     <x:t>JAN JOSEPH JAMERO</x:t>
   </x:si>
   <x:si>
-    <x:t>XIII | March 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -107,9 +105,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>XIII | January 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -146,9 +141,6 @@
     <x:t>1478245</x:t>
   </x:si>
   <x:si>
-    <x:t>XIII | March 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>CATV Station License (NEW)</x:t>
   </x:si>
   <x:si>
@@ -318,6 +310,24 @@
   </x:si>
   <x:si>
     <x:t>1516186</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEXTER AYENTO MORETO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n/a San Francisco St., Brgy. Sikatuna, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94-1PX-9554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1080-881</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516302</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -656,7 +666,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -671,6 +681,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -743,7 +756,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -779,6 +792,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1165,20 +1182,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45717</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1201,81 +1218,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45743.3040092824</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45537</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45743.3040092824</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45537</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>45743.3122342361</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45743.3122342361</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1294,44 +1311,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2434,20 +2451,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2470,173 +2487,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
+      <x:c r="F8" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G8" s="29" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H8" s="31">
+      <x:c r="H8" s="32">
         <x:v>46030.2246127662</x:v>
       </x:c>
-      <x:c r="I8" s="31">
+      <x:c r="I8" s="32">
         <x:v>46030.2246403009</x:v>
       </x:c>
-      <x:c r="J8" s="30" t="s">
+      <x:c r="J8" s="31" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46030.2605660764</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="33">
-        <x:v>46030.2605660764</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
+      <x:c r="B9" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>46036.0630976157</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46036.0631306944</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
-        <x:v>46036.0630976157</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>46036.0631306944</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="K9" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>46036.0820433218</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3738,20 +3755,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3774,537 +3791,537 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
+      <x:c r="H8" s="32">
+        <x:v>46111.1470208796</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46111.1470245139</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G8" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H8" s="31">
-        <x:v>46111.1470208796</x:v>
-      </x:c>
-      <x:c r="I8" s="31">
-        <x:v>46111.1470245139</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>97720</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="34">
         <x:v>46111.1717733681</x:v>
       </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
+      <x:c r="B9" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="29" t="s">
+      <x:c r="H9" s="32">
+        <x:v>46111.3583193056</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
-        <x:v>46111.3583193056</x:v>
-      </x:c>
-      <x:c r="I9" s="31">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="K9" s="33" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>46111.3723021991</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="B10" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
+      <x:c r="H10" s="32">
+        <x:v>46100.1079781713</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46100.1417990741</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46100.1079781713</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>46100.1417990741</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="K10" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="34">
         <x:v>46100.1612414352</x:v>
       </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="B11" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46100.0888710764</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46100.1424897801</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46100.0888710764</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46100.1424897801</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="K11" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="33">
+      <x:c r="L11" s="34">
         <x:v>46100.1669975463</x:v>
       </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
+      <x:c r="B12" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46100.1182232523</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46100.1416081713</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>46100.1182232523</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>46100.1416081713</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="K12" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="33">
+      <x:c r="L12" s="34">
         <x:v>46100.1503302546</x:v>
       </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
+      <x:c r="B13" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
+      <x:c r="H13" s="32">
+        <x:v>46100.1012338657</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46100.1420214352</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>46100.1012338657</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>46100.1420214352</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="K13" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="33">
+      <x:c r="L13" s="34">
         <x:v>46100.1632961806</x:v>
       </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
+      <x:c r="B14" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D14" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
+      <x:c r="H14" s="32">
+        <x:v>46100.1284434491</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46100.1411114583</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F14" s="29" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G14" s="29" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H14" s="31">
-        <x:v>46100.1284434491</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>46100.1411114583</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
+      <x:c r="K14" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L14" s="33">
+      <x:c r="L14" s="34">
         <x:v>46100.1586730671</x:v>
       </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s">
+      <x:c r="B15" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D15" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="29" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46112.1495942824</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46112.1682116435</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="F15" s="29" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G15" s="29" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H15" s="31">
-        <x:v>46112.1495942824</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>46112.1682116435</x:v>
-      </x:c>
-      <x:c r="J15" s="30" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
+      <x:c r="K15" s="33" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L15" s="33">
+      <x:c r="L15" s="34">
         <x:v>46112.2080237037</x:v>
       </x:c>
-      <x:c r="M15" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s">
+      <x:c r="B16" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D16" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46100.1227937384</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46100.1413909606</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F16" s="29" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G16" s="29" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H16" s="31">
-        <x:v>46100.1227937384</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>46100.1413909606</x:v>
-      </x:c>
-      <x:c r="J16" s="30" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
+      <x:c r="K16" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="33">
+      <x:c r="L16" s="34">
         <x:v>46100.1550834606</x:v>
       </x:c>
-      <x:c r="M16" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s">
+      <x:c r="B17" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D17" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E17" s="29" t="s">
+      <x:c r="H17" s="32">
+        <x:v>46100.0935301273</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46100.1422867824</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F17" s="29" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H17" s="31">
-        <x:v>46100.0935301273</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>46100.1422867824</x:v>
-      </x:c>
-      <x:c r="J17" s="30" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
+      <x:c r="K17" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L17" s="33">
+      <x:c r="L17" s="34">
         <x:v>46100.1651693866</x:v>
       </x:c>
-      <x:c r="M17" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s">
+      <x:c r="B18" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D18" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="29" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46093.1010420255</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>45374</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F18" s="29" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46093.1010420255</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>45374</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
+      <x:c r="K18" s="33" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L18" s="33">
+      <x:c r="L18" s="34">
         <x:v>46093.1172837847</x:v>
       </x:c>
-      <x:c r="M18" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="s"/>
-      <x:c r="D21" s="18" t="s"/>
-      <x:c r="E21" s="19" t="s"/>
-      <x:c r="F21" s="19" t="s"/>
+      <x:c r="B21" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="19" t="s"/>
+      <x:c r="D21" s="19" t="s"/>
+      <x:c r="E21" s="20" t="s"/>
+      <x:c r="F21" s="20" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="20" t="s">
+      <x:c r="B22" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C22" s="21" t="s"/>
-      <x:c r="D22" s="21" t="s"/>
-      <x:c r="E22" s="21" t="s"/>
-      <x:c r="F22" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C23" s="24" t="s"/>
-      <x:c r="D23" s="24" t="s"/>
-      <x:c r="E23" s="24" t="s"/>
-      <x:c r="F23" s="25" t="n">
+      <x:c r="B23" s="24" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="25" t="n">
+      <x:c r="B24" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C25" s="24" t="s"/>
-      <x:c r="D25" s="24" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="25" t="n">
+      <x:c r="B25" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="n">
+      <x:c r="B26" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="B27" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -5301,4 +5318,1273 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46118.0859375579</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46150</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46118.1095564468</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -328,6 +328,24 @@
   </x:si>
   <x:si>
     <x:t>1516302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to PURCHASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGATA MINING VENTURES,INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lawigan, Tubay, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIII-07999-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1081-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516304</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5490,102 +5508,134 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="30" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="30" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="32">
         <x:v>46118.0859375579</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="32">
         <x:v>46150</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="34">
         <x:v>46118.1095564468</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s"/>
+      <x:c r="E9" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>46118.2457655324</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46118.2457900694</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46118.2697333565</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="24" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6564,15 +6614,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -330,6 +330,66 @@
     <x:t>1516302</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILE CRAZE TELECOM INC.  (OPPO KIOSK) (BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CBN-GFK-12 GAISANO GRAND MALL, BRGY. 12 POB., City Of Cabadbaran, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIII-08111-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1103-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILE CRAZE TELECOM INC. (SAMSUNG KIOSK) (BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cCBN-GFK-13 GAISANO GRAND MALL, BRGY.poblacion 12, City Of Cabadbaran, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIII-08110-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1102-464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILE CRAZE TELECOM INC. (TECNO KIOSK) (BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRGY.POBLACION 12, City Of Cabadbaran, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIII-08108-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1101-840</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILE CRAZE TELECOM INC. (XIAOME KIOSK) BRANCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CBN-GFK-14 GAISANO GRAND MALL, BRGY.POBLACION 12, City Of Cabadbaran, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIII-08112-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1104-682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516322</x:t>
+  </x:si>
+  <x:si>
     <x:t>Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
@@ -346,6 +406,135 @@
   </x:si>
   <x:si>
     <x:t>1516304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARCITA APOLINARIA REYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Panlabuhan, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08067-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1088-229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANILO VICENTE NADONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Moto, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08075-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1095-048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EZEQUIEL REYES MIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08074-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1094-715</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERNANDO REYES DOLORES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Naliyagan, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08069-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1090-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516315</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLENN MONTES MANLANGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok-9, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08078-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1098-758</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516318</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JULIANA HAVANA ESCRIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Jandayugong, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08070-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1091-795</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBERTO PALMON AYALA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok-2, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08077-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1097-132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516319</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROMNICK CASAL IGNACIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sitio Tawilon, Poblacion, Loreto, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08079-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1099-556</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WENCESLAO ORLANDEZ REYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLMP-XIII-08073-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1093-636</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516316</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5547,110 +5736,611 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="D9" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s"/>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="F9" s="30" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="G9" s="30" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="H9" s="32">
+        <x:v>46120.1844251157</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46120.1844620486</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H9" s="32">
-        <x:v>46118.2457655324</x:v>
-      </x:c>
-      <x:c r="I9" s="32">
-        <x:v>46118.2457900694</x:v>
-      </x:c>
-      <x:c r="J9" s="31" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="K9" s="33" t="n">
-        <x:v>1710</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46118.2697333565</x:v>
+        <x:v>46120.2675123495</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46120.1809357755</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46120.180990625</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46120.2677879514</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46120.1772691204</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46120.1774708102</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>46120.2680576968</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="B12" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46120.1872445139</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46120.1873116204</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="34">
+        <x:v>46120.2671879514</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46118.2457655324</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46118.2457900694</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="n">
+        <x:v>1710</x:v>
+      </x:c>
+      <x:c r="L13" s="34">
+        <x:v>46118.2697333565</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46119.1363557639</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46119.4024510301</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="K14" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="34">
+        <x:v>46120.2066796875</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46119.1496079398</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.4042721991</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K15" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L15" s="34">
+        <x:v>46120.1632395602</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46119.147375544</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.4211153819</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K16" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L16" s="34">
+        <x:v>46120.1628406018</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46119.1392493403</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46119.4026281134</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="K17" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L17" s="34">
+        <x:v>46120.1983392245</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46119.1552351505</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46119.4032803009</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K18" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L18" s="34">
+        <x:v>46120.1647675232</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46119.1422446296</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46119.4022374537</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K19" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L19" s="34">
+        <x:v>46120.207101169</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46119.1531599306</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.403984375</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K20" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L20" s="34">
+        <x:v>46120.1636090856</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46119.1574735532</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.403066169</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="K21" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L21" s="34">
+        <x:v>46120.1653577778</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46119.1452747338</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.4028227894</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="K22" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L22" s="34">
+        <x:v>46120.1874508102</x:v>
+      </x:c>
+      <x:c r="M22" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C25" s="19" t="s"/>
+      <x:c r="D25" s="19" t="s"/>
+      <x:c r="E25" s="20" t="s"/>
+      <x:c r="F25" s="20" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="24" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="24" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B31" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6614,16 +7304,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B25:F25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -406,6 +406,36 @@
   </x:si>
   <x:si>
     <x:t>1516304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCVENURES MINING DEVELOPMENT CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-8, Panikian, City Of Tandag (Capital), Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIII-08232-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1106-950</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ST. JOSEPH CATHEDRAL DIOCESAN SHRINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>n/a E.Luna St., Brgy. Diego Silang, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NRSL-MM-0078-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1105-090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516327</x:t>
   </x:si>
   <x:si>
     <x:t>CARCITA APOLINARIA REYES</x:t>
@@ -5924,14 +5954,12 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="D14" s="31" t="s"/>
       <x:c r="E14" s="30" t="s">
         <x:v>128</x:v>
       </x:c>
@@ -5942,19 +5970,19 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.1363557639</x:v>
+        <x:v>46125.1134160069</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.4024510301</x:v>
+        <x:v>46125.1134349537</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46125.1559774537</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5962,13 +5990,13 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
       <x:c r="D15" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="30" t="s">
         <x:v>133</x:v>
@@ -5980,19 +6008,19 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.1496079398</x:v>
+        <x:v>46125.0306295139</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.4042721991</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -6009,28 +6037,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E16" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.147375544</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.4211153819</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -6041,34 +6069,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D17" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6079,13 +6107,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
         <x:v>148</x:v>
@@ -6094,10 +6122,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.1552351505</x:v>
+        <x:v>46119.147375544</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.4032803009</x:v>
+        <x:v>46119.4211153819</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>150</x:v>
@@ -6106,7 +6134,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6132,10 +6160,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.1422446296</x:v>
+        <x:v>46119.1392493403</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.4022374537</x:v>
+        <x:v>46119.4026281134</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>155</x:v>
@@ -6144,7 +6172,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6170,10 +6198,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.1531599306</x:v>
+        <x:v>46119.1552351505</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.403984375</x:v>
+        <x:v>46119.4032803009</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>160</x:v>
@@ -6182,7 +6210,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6208,10 +6236,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.1574735532</x:v>
+        <x:v>46119.1422446296</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.403066169</x:v>
+        <x:v>46119.4022374537</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>165</x:v>
@@ -6220,7 +6248,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.207101169</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6237,80 +6265,134 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E22" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.1531599306</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.403984375</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1636090856</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="18" t="s">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46119.1574735532</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.403066169</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K23" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L23" s="34">
+        <x:v>46120.1653577778</x:v>
+      </x:c>
+      <x:c r="M23" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F24" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>46119.1452747338</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46119.4028227894</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="K24" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L24" s="34">
+        <x:v>46120.1874508102</x:v>
+      </x:c>
+      <x:c r="M24" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C25" s="19" t="s"/>
-      <x:c r="D25" s="19" t="s"/>
-      <x:c r="E25" s="20" t="s"/>
-      <x:c r="F25" s="20" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="21" t="s">
+      <x:c r="C27" s="19" t="s"/>
+      <x:c r="D27" s="19" t="s"/>
+      <x:c r="E27" s="20" t="s"/>
+      <x:c r="F27" s="20" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="s">
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="24" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C29" s="25" t="s"/>
       <x:c r="D29" s="25" t="s"/>
@@ -6321,29 +6403,59 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C30" s="25" t="s"/>
       <x:c r="D30" s="25" t="s"/>
       <x:c r="E30" s="25" t="s"/>
       <x:c r="F30" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="24" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C32" s="25" t="s"/>
+      <x:c r="D32" s="25" t="s"/>
+      <x:c r="E32" s="25" t="s"/>
+      <x:c r="F32" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C33" s="25" t="s"/>
+      <x:c r="D33" s="25" t="s"/>
+      <x:c r="E33" s="25" t="s"/>
+      <x:c r="F33" s="26" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="27" t="s">
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7304,18 +7416,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B25:F25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -565,6 +565,39 @@
   </x:si>
   <x:si>
     <x:t>1516316</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JIMMY PALABRICA TOTESORA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOONGAN, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23-SROPVII-18354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1107-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516330</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNICOM MOBLIE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>poblacion 2, Santiago, Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-MM-0001-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1108-443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516332</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -6368,98 +6401,192 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="18" t="s">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="30" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F25" s="30" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>46125.1213370023</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46043</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K25" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L25" s="34">
+        <x:v>46125.157450625</x:v>
+      </x:c>
+      <x:c r="M25" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D26" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F26" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K26" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M26" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C27" s="19" t="s"/>
-      <x:c r="D27" s="19" t="s"/>
-      <x:c r="E27" s="20" t="s"/>
-      <x:c r="F27" s="20" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="21" t="s">
+      <x:c r="C29" s="19" t="s"/>
+      <x:c r="D29" s="19" t="s"/>
+      <x:c r="E29" s="20" t="s"/>
+      <x:c r="F29" s="20" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="s">
+      <x:c r="C30" s="22" t="s"/>
+      <x:c r="D30" s="22" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C30" s="25" t="s"/>
-      <x:c r="D30" s="25" t="s"/>
-      <x:c r="E30" s="25" t="s"/>
-      <x:c r="F30" s="26" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="24" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C31" s="25" t="s"/>
       <x:c r="D31" s="25" t="s"/>
       <x:c r="E31" s="25" t="s"/>
       <x:c r="F31" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C32" s="25" t="s"/>
       <x:c r="D32" s="25" t="s"/>
       <x:c r="E32" s="25" t="s"/>
       <x:c r="F32" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C33" s="25" t="s"/>
       <x:c r="D33" s="25" t="s"/>
       <x:c r="E33" s="25" t="s"/>
       <x:c r="F33" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C34" s="25" t="s"/>
+      <x:c r="D34" s="25" t="s"/>
+      <x:c r="E34" s="25" t="s"/>
+      <x:c r="F34" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="s"/>
+      <x:c r="D35" s="25" t="s"/>
+      <x:c r="E35" s="25" t="s"/>
+      <x:c r="F35" s="26" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="27" t="s">
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C36" s="25" t="s"/>
+      <x:c r="D36" s="25" t="s"/>
+      <x:c r="E36" s="25" t="s"/>
+      <x:c r="F36" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="24" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C37" s="25" t="s"/>
+      <x:c r="D37" s="25" t="s"/>
+      <x:c r="E37" s="25" t="s"/>
+      <x:c r="F37" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B38" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C38" s="28" t="s"/>
+      <x:c r="D38" s="28" t="s"/>
+      <x:c r="E38" s="28" t="s"/>
+      <x:c r="F38" s="29" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7416,19 +7543,21 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
+  <x:mergeCells count="14">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -388,6 +388,33 @@
   </x:si>
   <x:si>
     <x:t>1516322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTERPACE CORPORATION (GAISANO MALL BUTUAN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO MALL BUTUAN, Imadejas, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WDN-MM-00015-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1110-190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-MM-0017-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1109-429</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516335</x:t>
   </x:si>
   <x:si>
     <x:t>Permit to PURCHASE</x:t>
@@ -5956,7 +5983,9 @@
       <x:c r="C13" s="30" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s"/>
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E13" s="30" t="s">
         <x:v>123</x:v>
       </x:c>
@@ -5967,19 +5996,19 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.2457655324</x:v>
+        <x:v>46125.3805303819</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.2457900694</x:v>
+        <x:v>46140</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
-        <x:v>1710</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.2697333565</x:v>
+        <x:v>46125.4137300926</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5990,32 +6019,34 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="G14" s="30" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="H14" s="32">
+        <x:v>46125.3770215625</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46140</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H14" s="32">
-        <x:v>46125.1134160069</x:v>
-      </x:c>
-      <x:c r="I14" s="32">
-        <x:v>46125.1134349537</x:v>
-      </x:c>
-      <x:c r="J14" s="31" t="s">
-        <x:v>131</x:v>
-      </x:c>
       <x:c r="K14" s="33" t="n">
-        <x:v>1374</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46125.1559774537</x:v>
+        <x:v>46125.4131163889</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -6023,37 +6054,35 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s"/>
+      <x:c r="E15" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="F15" s="30" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="G15" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46118.2457655324</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46118.2457900694</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="K15" s="33" t="n">
-        <x:v>3006</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46125.1001882292</x:v>
+        <x:v>46118.2697333565</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -6061,37 +6090,35 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="30" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="F16" s="30" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="G16" s="30" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46125.1134160069</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46125.1134349537</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.1363557639</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.4024510301</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="K16" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46125.1559774537</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -6099,37 +6126,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="F17" s="30" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="G17" s="30" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="H17" s="32">
+        <x:v>46125.0306295139</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H17" s="32">
-        <x:v>46119.1496079398</x:v>
-      </x:c>
-      <x:c r="I17" s="32">
-        <x:v>46119.4042721991</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="K17" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6140,13 +6167,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
         <x:v>148</x:v>
@@ -6155,10 +6182,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.147375544</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.4211153819</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>150</x:v>
@@ -6167,7 +6194,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6193,10 +6220,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>155</x:v>
@@ -6205,7 +6232,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6222,28 +6249,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E20" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F20" s="30" t="s">
+      <x:c r="G20" s="30" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46119.147375544</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.4211153819</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.1552351505</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.4032803009</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6254,34 +6281,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D21" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E21" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="s">
+      <x:c r="G21" s="30" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="H21" s="32">
+        <x:v>46119.1392493403</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.4026281134</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.1422446296</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.4022374537</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6292,34 +6319,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D22" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E22" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="G22" s="30" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46119.1552351505</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.4032803009</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.1531599306</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.403984375</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6330,34 +6357,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D23" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E23" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="s">
+      <x:c r="G23" s="30" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="H23" s="32">
+        <x:v>46119.1422446296</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.4022374537</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46119.1574735532</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46119.403066169</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.207101169</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6368,13 +6395,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D24" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E24" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
         <x:v>177</x:v>
@@ -6383,10 +6410,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.1531599306</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.403984375</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>179</x:v>
@@ -6395,7 +6422,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1636090856</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6403,13 +6430,13 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s">
         <x:v>180</x:v>
       </x:c>
       <x:c r="D25" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E25" s="30" t="s">
         <x:v>181</x:v>
@@ -6421,10 +6448,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46125.1213370023</x:v>
+        <x:v>46119.1574735532</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46043</x:v>
+        <x:v>46119.403066169</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
         <x:v>184</x:v>
@@ -6433,7 +6460,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46125.157450625</x:v>
+        <x:v>46120.1653577778</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6441,133 +6468,187 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s">
+      <x:c r="D26" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E26" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F26" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E26" s="30" t="s">
+      <x:c r="G26" s="30" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46119.1452747338</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46119.4028227894</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46125.2289653241</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46124</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="K26" s="33" t="n">
-        <x:v>3780</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46125.2566478009</x:v>
+        <x:v>46120.1874508102</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="18" t="s">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E27" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F27" s="30" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46125.1213370023</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46043</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="K27" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L27" s="34">
+        <x:v>46125.157450625</x:v>
+      </x:c>
+      <x:c r="M27" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F28" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="K28" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L28" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M28" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C29" s="19" t="s"/>
-      <x:c r="D29" s="19" t="s"/>
-      <x:c r="E29" s="20" t="s"/>
-      <x:c r="F29" s="20" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="21" t="s">
+      <x:c r="C31" s="19" t="s"/>
+      <x:c r="D31" s="19" t="s"/>
+      <x:c r="E31" s="20" t="s"/>
+      <x:c r="F31" s="20" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B32" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C30" s="22" t="s"/>
-      <x:c r="D30" s="22" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="23" t="s">
+      <x:c r="C32" s="22" t="s"/>
+      <x:c r="D32" s="22" t="s"/>
+      <x:c r="E32" s="22" t="s"/>
+      <x:c r="F32" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C32" s="25" t="s"/>
-      <x:c r="D32" s="25" t="s"/>
-      <x:c r="E32" s="25" t="s"/>
-      <x:c r="F32" s="26" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="24" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C33" s="25" t="s"/>
       <x:c r="D33" s="25" t="s"/>
       <x:c r="E33" s="25" t="s"/>
       <x:c r="F33" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="25" t="s"/>
       <x:c r="D34" s="25" t="s"/>
       <x:c r="E34" s="25" t="s"/>
       <x:c r="F34" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C35" s="25" t="s"/>
       <x:c r="D35" s="25" t="s"/>
       <x:c r="E35" s="25" t="s"/>
       <x:c r="F35" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C36" s="25" t="s"/>
       <x:c r="D36" s="25" t="s"/>
       <x:c r="E36" s="25" t="s"/>
       <x:c r="F36" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="24" t="s">
-        <x:v>185</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="25" t="s"/>
       <x:c r="D37" s="25" t="s"/>
@@ -6576,20 +6657,50 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B38" s="27" t="s">
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C38" s="25" t="s"/>
+      <x:c r="D38" s="25" t="s"/>
+      <x:c r="E38" s="25" t="s"/>
+      <x:c r="F38" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C39" s="25" t="s"/>
+      <x:c r="D39" s="25" t="s"/>
+      <x:c r="E39" s="25" t="s"/>
+      <x:c r="F39" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="24" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C40" s="25" t="s"/>
+      <x:c r="D40" s="25" t="s"/>
+      <x:c r="E40" s="25" t="s"/>
+      <x:c r="F40" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C38" s="28" t="s"/>
-      <x:c r="D38" s="28" t="s"/>
-      <x:c r="E38" s="28" t="s"/>
-      <x:c r="F38" s="29" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C41" s="28" t="s"/>
+      <x:c r="D41" s="28" t="s"/>
+      <x:c r="E41" s="28" t="s"/>
+      <x:c r="F41" s="29" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7543,14 +7654,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="14">
+  <x:mergeCells count="15">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
-    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B31:F31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
@@ -7558,6 +7667,9 @@
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -310,6 +310,93 @@
   </x:si>
   <x:si>
     <x:t>1516186</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Operator Certificate (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMBERLY PETEROS SOTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOTO, City Of Tandag (Capital), Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08366-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1116-702</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATERNO REBUYON COLASTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUEZON, City Of Tandag (Capital), Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08367-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1117-892</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROLENDES CALIHAT VALLESCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONGTOD, City Of Tandag (Capital), Surigao Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08357-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1112-167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMBERLY P. SOTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08364-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1115-390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516348</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATERNO R. COLASTE, JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08363-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1114-908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROLENDES C. VALLESCAS, JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08362-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1113-210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516345</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
@@ -5794,7 +5881,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D8" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E8" s="30" t="s">
         <x:v>97</x:v>
@@ -5806,19 +5893,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H8" s="32">
-        <x:v>46118.0859375579</x:v>
+        <x:v>46127.1008034144</x:v>
       </x:c>
       <x:c r="I8" s="32">
-        <x:v>46150</x:v>
+        <x:v>46127.152407338</x:v>
       </x:c>
       <x:c r="J8" s="31" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K8" s="33" t="n">
-        <x:v>390</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="34">
-        <x:v>46118.1095564468</x:v>
+        <x:v>46127.2663131018</x:v>
       </x:c>
       <x:c r="M8" s="30" t="s">
         <x:v>21</x:v>
@@ -5826,7 +5913,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="30" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C9" s="30" t="s">
         <x:v>101</x:v>
@@ -5844,19 +5931,19 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46120.1844251157</x:v>
+        <x:v>46127.1031398843</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46120.1844620486</x:v>
+        <x:v>46127.151645162</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46120.2675123495</x:v>
+        <x:v>46127.2649922801</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -5864,7 +5951,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="30" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C10" s="30" t="s">
         <x:v>106</x:v>
@@ -5882,19 +5969,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46120.1809357755</x:v>
+        <x:v>46127.0508113889</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46120.180990625</x:v>
+        <x:v>46127.1521238079</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46120.2677879514</x:v>
+        <x:v>46127.2659745833</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5902,16 +5989,14 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="30" t="s">
-        <x:v>26</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C11" s="30" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s"/>
       <x:c r="E11" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
         <x:v>113</x:v>
@@ -5920,19 +6005,19 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46120.1772691204</x:v>
+        <x:v>46127.0960319676</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46120.1774708102</x:v>
+        <x:v>46127.1525701505</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46120.2680576968</x:v>
+        <x:v>46127.2673643403</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5940,37 +6025,35 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="30" t="s">
-        <x:v>26</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C12" s="30" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="D12" s="31" t="s"/>
       <x:c r="E12" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46127.0942539931</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46127.1508667708</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H12" s="32">
-        <x:v>46120.1872445139</x:v>
-      </x:c>
-      <x:c r="I12" s="32">
-        <x:v>46120.1873116204</x:v>
-      </x:c>
-      <x:c r="J12" s="31" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="K12" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46120.2671879514</x:v>
+        <x:v>46127.2644301042</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5978,37 +6061,35 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s"/>
+      <x:c r="E13" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="G13" s="30" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="H13" s="32">
+        <x:v>46127.0914937616</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46127.1519132986</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G13" s="30" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H13" s="32">
-        <x:v>46125.3805303819</x:v>
-      </x:c>
-      <x:c r="I13" s="32">
-        <x:v>46140</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="K13" s="33" t="n">
-        <x:v>1950</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46125.4137300926</x:v>
+        <x:v>46127.2655630324</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -6016,16 +6097,16 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D14" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
         <x:v>127</x:v>
@@ -6034,19 +6115,19 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46125.3770215625</x:v>
+        <x:v>46118.0859375579</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46140</x:v>
+        <x:v>46150</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
-        <x:v>4030</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46125.4131163889</x:v>
+        <x:v>46118.1095564468</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -6054,35 +6135,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="30" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="D15" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="F15" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="G15" s="30" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46120.1844251157</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46120.1844620486</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46118.2457655324</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46118.2457900694</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>135</x:v>
-      </x:c>
       <x:c r="K15" s="33" t="n">
-        <x:v>1710</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.2697333565</x:v>
+        <x:v>46120.2675123495</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -6090,35 +6173,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="F16" s="30" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="G16" s="30" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46120.1809357755</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46120.180990625</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46125.1134160069</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46125.1134349537</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>140</x:v>
-      </x:c>
       <x:c r="K16" s="33" t="n">
-        <x:v>1374</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46125.1559774537</x:v>
+        <x:v>46120.2677879514</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -6126,37 +6211,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="F17" s="30" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="G17" s="30" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="H17" s="32">
+        <x:v>46120.1772691204</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46120.1774708102</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H17" s="32">
-        <x:v>46125.0306295139</x:v>
-      </x:c>
-      <x:c r="I17" s="32">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="s">
-        <x:v>145</x:v>
-      </x:c>
       <x:c r="K17" s="33" t="n">
-        <x:v>3006</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46125.1001882292</x:v>
+        <x:v>46120.2680576968</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6164,37 +6249,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="G18" s="30" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46120.1872445139</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46120.1873116204</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.1363557639</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.4024510301</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>150</x:v>
-      </x:c>
       <x:c r="K18" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46120.2671879514</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6202,13 +6287,13 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C19" s="30" t="s">
         <x:v>151</x:v>
       </x:c>
       <x:c r="D19" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="30" t="s">
         <x:v>152</x:v>
@@ -6220,19 +6305,19 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.1496079398</x:v>
+        <x:v>46125.3805303819</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.4042721991</x:v>
+        <x:v>46140</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>155</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46125.4137300926</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6240,37 +6325,37 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C20" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D20" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="30" t="s">
         <x:v>152</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46125.3770215625</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46140</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.147375544</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.4211153819</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>159</x:v>
-      </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46125.4131163889</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6278,14 +6363,12 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C21" s="30" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="D21" s="31" t="s"/>
       <x:c r="E21" s="30" t="s">
         <x:v>161</x:v>
       </x:c>
@@ -6296,19 +6379,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46118.2457655324</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46118.2457900694</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>164</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46118.2697333565</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6316,14 +6399,12 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C22" s="30" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="D22" s="31" t="s"/>
       <x:c r="E22" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
@@ -6334,19 +6415,19 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.1552351505</x:v>
+        <x:v>46125.1134160069</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.4032803009</x:v>
+        <x:v>46125.1134349537</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>169</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46125.1559774537</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6354,13 +6435,13 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
         <x:v>170</x:v>
       </x:c>
       <x:c r="D23" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="30" t="s">
         <x:v>171</x:v>
@@ -6372,19 +6453,19 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.1422446296</x:v>
+        <x:v>46125.0306295139</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.4022374537</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
         <x:v>174</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6410,10 +6491,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.1531599306</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.403984375</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>179</x:v>
@@ -6422,7 +6503,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6448,10 +6529,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.1574735532</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.403066169</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
         <x:v>184</x:v>
@@ -6460,7 +6541,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6477,7 +6558,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E26" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
         <x:v>186</x:v>
@@ -6486,10 +6567,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.147375544</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.4211153819</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
         <x:v>188</x:v>
@@ -6498,7 +6579,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6506,13 +6587,13 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s">
         <x:v>189</x:v>
       </x:c>
       <x:c r="D27" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E27" s="30" t="s">
         <x:v>190</x:v>
@@ -6524,10 +6605,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46125.1213370023</x:v>
+        <x:v>46119.1392493403</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46043</x:v>
+        <x:v>46119.4026281134</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
         <x:v>193</x:v>
@@ -6536,7 +6617,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46125.157450625</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6544,171 +6625,413 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="C28" s="30" t="s">
+      <x:c r="D28" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E28" s="30" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D28" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E28" s="30" t="s">
+      <x:c r="F28" s="30" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F28" s="30" t="s">
+      <x:c r="G28" s="30" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46119.1552351505</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.4032803009</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46125.2289653241</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46124</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="K28" s="33" t="n">
-        <x:v>3780</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46125.2566478009</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D29" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E29" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F29" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>46119.1422446296</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46119.4022374537</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="K29" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L29" s="34">
+        <x:v>46120.207101169</x:v>
+      </x:c>
+      <x:c r="M29" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E30" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F30" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>46119.1531599306</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46119.403984375</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="K30" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L30" s="34">
+        <x:v>46120.1636090856</x:v>
+      </x:c>
+      <x:c r="M30" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="18" t="s">
+      <x:c r="B31" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E31" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F31" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>46119.1574735532</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46119.403066169</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="K31" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L31" s="34">
+        <x:v>46120.1653577778</x:v>
+      </x:c>
+      <x:c r="M31" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F32" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H32" s="32">
+        <x:v>46119.1452747338</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46119.4028227894</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="K32" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L32" s="34">
+        <x:v>46120.1874508102</x:v>
+      </x:c>
+      <x:c r="M32" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E33" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F33" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H33" s="32">
+        <x:v>46125.1213370023</x:v>
+      </x:c>
+      <x:c r="I33" s="32">
+        <x:v>46043</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="K33" s="33" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L33" s="34">
+        <x:v>46125.157450625</x:v>
+      </x:c>
+      <x:c r="M33" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E34" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F34" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="K34" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L34" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M34" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C31" s="19" t="s"/>
-      <x:c r="D31" s="19" t="s"/>
-      <x:c r="E31" s="20" t="s"/>
-      <x:c r="F31" s="20" t="s"/>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B32" s="21" t="s">
+      <x:c r="C37" s="19" t="s"/>
+      <x:c r="D37" s="19" t="s"/>
+      <x:c r="E37" s="20" t="s"/>
+      <x:c r="F37" s="20" t="s"/>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B38" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C32" s="22" t="s"/>
-      <x:c r="D32" s="22" t="s"/>
-      <x:c r="E32" s="22" t="s"/>
-      <x:c r="F32" s="23" t="s">
+      <x:c r="C38" s="22" t="s"/>
+      <x:c r="D38" s="22" t="s"/>
+      <x:c r="E38" s="22" t="s"/>
+      <x:c r="F38" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C33" s="25" t="s"/>
-      <x:c r="D33" s="25" t="s"/>
-      <x:c r="E33" s="25" t="s"/>
-      <x:c r="F33" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C34" s="25" t="s"/>
-      <x:c r="D34" s="25" t="s"/>
-      <x:c r="E34" s="25" t="s"/>
-      <x:c r="F34" s="26" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="24" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C35" s="25" t="s"/>
-      <x:c r="D35" s="25" t="s"/>
-      <x:c r="E35" s="25" t="s"/>
-      <x:c r="F35" s="26" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="24" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C36" s="25" t="s"/>
-      <x:c r="D36" s="25" t="s"/>
-      <x:c r="E36" s="25" t="s"/>
-      <x:c r="F36" s="26" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="24" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C37" s="25" t="s"/>
-      <x:c r="D37" s="25" t="s"/>
-      <x:c r="E37" s="25" t="s"/>
-      <x:c r="F37" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="24" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C38" s="25" t="s"/>
-      <x:c r="D38" s="25" t="s"/>
-      <x:c r="E38" s="25" t="s"/>
-      <x:c r="F38" s="26" t="n">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="25" t="s"/>
       <x:c r="D39" s="25" t="s"/>
       <x:c r="E39" s="25" t="s"/>
       <x:c r="F39" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
       <x:c r="B40" s="24" t="s">
-        <x:v>194</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C40" s="25" t="s"/>
       <x:c r="D40" s="25" t="s"/>
       <x:c r="E40" s="25" t="s"/>
       <x:c r="F40" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="24" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C41" s="25" t="s"/>
+      <x:c r="D41" s="25" t="s"/>
+      <x:c r="E41" s="25" t="s"/>
+      <x:c r="F41" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="27" t="s">
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C42" s="25" t="s"/>
+      <x:c r="D42" s="25" t="s"/>
+      <x:c r="E42" s="25" t="s"/>
+      <x:c r="F42" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B43" s="24" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="s"/>
+      <x:c r="D43" s="25" t="s"/>
+      <x:c r="E43" s="25" t="s"/>
+      <x:c r="F43" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B44" s="24" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C44" s="25" t="s"/>
+      <x:c r="D44" s="25" t="s"/>
+      <x:c r="E44" s="25" t="s"/>
+      <x:c r="F44" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B45" s="24" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C45" s="25" t="s"/>
+      <x:c r="D45" s="25" t="s"/>
+      <x:c r="E45" s="25" t="s"/>
+      <x:c r="F45" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C46" s="25" t="s"/>
+      <x:c r="D46" s="25" t="s"/>
+      <x:c r="E46" s="25" t="s"/>
+      <x:c r="F46" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C47" s="25" t="s"/>
+      <x:c r="D47" s="25" t="s"/>
+      <x:c r="E47" s="25" t="s"/>
+      <x:c r="F47" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="24" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C48" s="25" t="s"/>
+      <x:c r="D48" s="25" t="s"/>
+      <x:c r="E48" s="25" t="s"/>
+      <x:c r="F48" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B49" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C41" s="28" t="s"/>
-      <x:c r="D41" s="28" t="s"/>
-      <x:c r="E41" s="28" t="s"/>
-      <x:c r="F41" s="29" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7654,22 +7977,24 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="15">
+  <x:mergeCells count="17">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B31:F31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B37:F37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B44:E44"/>
+    <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -535,6 +535,24 @@
   </x:si>
   <x:si>
     <x:t>1516329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRGY. AFGA, SIBAGAT, AGUSAN DEL SUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK-2, AFGA, Sibagat, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FX-ROXIII-08416-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1118-881</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516349</x:t>
   </x:si>
   <x:si>
     <x:t>ST. JOSEPH CATHEDRAL DIOCESAN SHRINE</x:t>
@@ -6435,37 +6453,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D23" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E23" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46127.3855537963</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46215</x:v>
+        <x:v>46127.3855756134</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>3006</x:v>
+        <x:v>7376</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46125.1001882292</x:v>
+        <x:v>46127.4285094444</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6473,37 +6491,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C24" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D24" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.1363557639</x:v>
+        <x:v>46125.0306295139</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.4024510301</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6514,34 +6532,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D25" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E25" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.1496079398</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.4042721991</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6552,34 +6570,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D26" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E26" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.147375544</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.4211153819</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>188</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6590,34 +6608,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D27" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E27" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46119.147375544</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46119.4211153819</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6628,34 +6646,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D28" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E28" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.1552351505</x:v>
+        <x:v>46119.1392493403</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.4032803009</x:v>
+        <x:v>46119.4026281134</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6666,34 +6684,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D29" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.1422446296</x:v>
+        <x:v>46119.1552351505</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.4022374537</x:v>
+        <x:v>46119.4032803009</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6704,34 +6722,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D30" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E30" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.1531599306</x:v>
+        <x:v>46119.1422446296</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.403984375</x:v>
+        <x:v>46119.4022374537</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.207101169</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6742,34 +6760,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D31" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E31" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.1574735532</x:v>
+        <x:v>46119.1531599306</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.403066169</x:v>
+        <x:v>46119.403984375</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.1636090856</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6780,34 +6798,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D32" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E32" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.1574735532</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.403066169</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1653577778</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6815,37 +6833,37 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="30" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D33" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E33" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46125.1213370023</x:v>
+        <x:v>46119.1452747338</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46043</x:v>
+        <x:v>46119.4028227894</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46125.157450625</x:v>
+        <x:v>46120.1874508102</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6853,7 +6871,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="30" t="s">
         <x:v>224</x:v>
@@ -6871,60 +6889,87 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46125.2289653241</x:v>
+        <x:v>46125.1213370023</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46124</x:v>
+        <x:v>46043</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
         <x:v>228</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
-        <x:v>3780</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46125.2566478009</x:v>
+        <x:v>46125.157450625</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="30" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F35" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H35" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K35" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L35" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M35" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="18" t="s">
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C37" s="19" t="s"/>
-      <x:c r="D37" s="19" t="s"/>
-      <x:c r="E37" s="20" t="s"/>
-      <x:c r="F37" s="20" t="s"/>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B38" s="21" t="s">
+      <x:c r="C38" s="19" t="s"/>
+      <x:c r="D38" s="19" t="s"/>
+      <x:c r="E38" s="20" t="s"/>
+      <x:c r="F38" s="20" t="s"/>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B39" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C38" s="22" t="s"/>
-      <x:c r="D38" s="22" t="s"/>
-      <x:c r="E38" s="22" t="s"/>
-      <x:c r="F38" s="23" t="s">
+      <x:c r="C39" s="22" t="s"/>
+      <x:c r="D39" s="22" t="s"/>
+      <x:c r="E39" s="22" t="s"/>
+      <x:c r="F39" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C39" s="25" t="s"/>
-      <x:c r="D39" s="25" t="s"/>
-      <x:c r="E39" s="25" t="s"/>
-      <x:c r="F39" s="26" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
       <x:c r="B40" s="24" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C40" s="25" t="s"/>
       <x:c r="D40" s="25" t="s"/>
@@ -6935,40 +6980,40 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
       <x:c r="B41" s="24" t="s">
-        <x:v>124</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C41" s="25" t="s"/>
       <x:c r="D41" s="25" t="s"/>
       <x:c r="E41" s="25" t="s"/>
       <x:c r="F41" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
       <x:c r="B42" s="24" t="s">
-        <x:v>26</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C42" s="25" t="s"/>
       <x:c r="D42" s="25" t="s"/>
       <x:c r="E42" s="25" t="s"/>
       <x:c r="F42" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="18" customHeight="1">
       <x:c r="B43" s="24" t="s">
-        <x:v>150</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="25" t="s"/>
       <x:c r="D43" s="25" t="s"/>
       <x:c r="E43" s="25" t="s"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
       <x:c r="B44" s="24" t="s">
-        <x:v>159</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C44" s="25" t="s"/>
       <x:c r="D44" s="25" t="s"/>
@@ -6979,29 +7024,29 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
       <x:c r="B45" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C45" s="25" t="s"/>
       <x:c r="D45" s="25" t="s"/>
       <x:c r="E45" s="25" t="s"/>
       <x:c r="F45" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C46" s="25" t="s"/>
       <x:c r="D46" s="25" t="s"/>
       <x:c r="E46" s="25" t="s"/>
       <x:c r="F46" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C47" s="25" t="s"/>
       <x:c r="D47" s="25" t="s"/>
@@ -7012,28 +7057,48 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="24" t="s">
-        <x:v>223</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C48" s="25" t="s"/>
       <x:c r="D48" s="25" t="s"/>
       <x:c r="E48" s="25" t="s"/>
       <x:c r="F48" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C49" s="25" t="s"/>
+      <x:c r="D49" s="25" t="s"/>
+      <x:c r="E49" s="25" t="s"/>
+      <x:c r="F49" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B49" s="27" t="s">
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="24" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C50" s="25" t="s"/>
+      <x:c r="D50" s="25" t="s"/>
+      <x:c r="E50" s="25" t="s"/>
+      <x:c r="F50" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B51" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7977,13 +8042,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="17">
+  <x:mergeCells count="18">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B37:F37"/>
-    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B38:F38"/>
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
@@ -7995,6 +8059,8 @@
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -486,6 +486,15 @@
     <x:t>GAISANO MALL BUTUAN, Imadejas, Butuan City (Capital), Agusan Del Norte</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-MM-0017-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1109-429</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516335</x:t>
+  </x:si>
+  <x:si>
     <x:t>WDN-MM-00015-21</x:t>
   </x:si>
   <x:si>
@@ -495,13 +504,22 @@
     <x:t>1516334</x:t>
   </x:si>
   <x:si>
-    <x:t>MPDP-MM-0017-21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70-4-2026-1109-429</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1516335</x:t>
+    <x:t>Duplicate Copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LGU - VERUELA, AGUSAN DEL SUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK 5, POBLACION, Veruela, Agusan Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08471-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1120-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516356</x:t>
   </x:si>
   <x:si>
     <x:t>Permit to PURCHASE</x:t>
@@ -6323,7 +6341,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46125.3805303819</x:v>
+        <x:v>46125.3770215625</x:v>
       </x:c>
       <x:c r="I19" s="32">
         <x:v>46140</x:v>
@@ -6332,10 +6350,10 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>1950</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46125.4137300926</x:v>
+        <x:v>46125.4131163889</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6361,7 +6379,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46125.3770215625</x:v>
+        <x:v>46125.3805303819</x:v>
       </x:c>
       <x:c r="I20" s="32">
         <x:v>46140</x:v>
@@ -6370,10 +6388,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>4030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46125.4131163889</x:v>
+        <x:v>46125.4137300926</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6397,19 +6415,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.2457655324</x:v>
+        <x:v>46128.2754106944</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.2457900694</x:v>
+        <x:v>46128.2754107639</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>164</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
-        <x:v>1710</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.2697333565</x:v>
+        <x:v>46128.2984009838</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6417,35 +6435,35 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C22" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D22" s="31" t="s"/>
       <x:c r="E22" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46125.1134160069</x:v>
+        <x:v>46118.2457655324</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46125.1134349537</x:v>
+        <x:v>46118.2457900694</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
-        <x:v>1374</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46125.1559774537</x:v>
+        <x:v>46118.2697333565</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6453,14 +6471,12 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
+      <x:c r="D23" s="31" t="s"/>
       <x:c r="E23" s="30" t="s">
         <x:v>172</x:v>
       </x:c>
@@ -6471,19 +6487,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46127.3855537963</x:v>
+        <x:v>46125.1134160069</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46127.3855756134</x:v>
+        <x:v>46125.1134349537</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
         <x:v>175</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>7376</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46127.4285094444</x:v>
+        <x:v>46125.1559774537</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6491,37 +6507,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C24" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D24" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E24" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46127.3855537963</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46215</x:v>
+        <x:v>46127.3855756134</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
-        <x:v>3006</x:v>
+        <x:v>7376</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46125.1001882292</x:v>
+        <x:v>46127.4285094444</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6529,37 +6545,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D25" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.1363557639</x:v>
+        <x:v>46125.0306295139</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.4024510301</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6570,34 +6586,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D26" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E26" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.1496079398</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.4042721991</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6608,34 +6624,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D27" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E27" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.147375544</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.4211153819</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6646,34 +6662,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D28" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E28" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46119.147375544</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46119.4211153819</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6684,34 +6700,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D29" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.1552351505</x:v>
+        <x:v>46119.1392493403</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.4032803009</x:v>
+        <x:v>46119.4026281134</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6722,34 +6738,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D30" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E30" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.1422446296</x:v>
+        <x:v>46119.1552351505</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.4022374537</x:v>
+        <x:v>46119.4032803009</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6760,34 +6776,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D31" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E31" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.1531599306</x:v>
+        <x:v>46119.1422446296</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.403984375</x:v>
+        <x:v>46119.4022374537</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.207101169</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6798,34 +6814,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D32" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E32" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.1574735532</x:v>
+        <x:v>46119.1531599306</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.403066169</x:v>
+        <x:v>46119.403984375</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.1636090856</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6836,34 +6852,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D33" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E33" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.1574735532</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.403066169</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1653577778</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6871,37 +6887,37 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C34" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D34" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E34" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46125.1213370023</x:v>
+        <x:v>46119.1452747338</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46043</x:v>
+        <x:v>46119.4028227894</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46125.157450625</x:v>
+        <x:v>46120.1874508102</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6909,7 +6925,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="30" t="s">
         <x:v>230</x:v>
@@ -6927,60 +6943,87 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46125.2289653241</x:v>
+        <x:v>46125.1213370023</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46124</x:v>
+        <x:v>46043</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
         <x:v>234</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
-        <x:v>3780</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46125.2566478009</x:v>
+        <x:v>46125.157450625</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="30" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D36" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E36" s="30" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F36" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H36" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K36" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L36" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M36" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="18" t="s">
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C38" s="19" t="s"/>
-      <x:c r="D38" s="19" t="s"/>
-      <x:c r="E38" s="20" t="s"/>
-      <x:c r="F38" s="20" t="s"/>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B39" s="21" t="s">
+      <x:c r="C39" s="19" t="s"/>
+      <x:c r="D39" s="19" t="s"/>
+      <x:c r="E39" s="20" t="s"/>
+      <x:c r="F39" s="20" t="s"/>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B40" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C39" s="22" t="s"/>
-      <x:c r="D39" s="22" t="s"/>
-      <x:c r="E39" s="22" t="s"/>
-      <x:c r="F39" s="23" t="s">
+      <x:c r="C40" s="22" t="s"/>
+      <x:c r="D40" s="22" t="s"/>
+      <x:c r="E40" s="22" t="s"/>
+      <x:c r="F40" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C40" s="25" t="s"/>
-      <x:c r="D40" s="25" t="s"/>
-      <x:c r="E40" s="25" t="s"/>
-      <x:c r="F40" s="26" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
       <x:c r="B41" s="24" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C41" s="25" t="s"/>
       <x:c r="D41" s="25" t="s"/>
@@ -6991,40 +7034,40 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
       <x:c r="B42" s="24" t="s">
-        <x:v>124</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C42" s="25" t="s"/>
       <x:c r="D42" s="25" t="s"/>
       <x:c r="E42" s="25" t="s"/>
       <x:c r="F42" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="18" customHeight="1">
       <x:c r="B43" s="24" t="s">
-        <x:v>26</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C43" s="25" t="s"/>
       <x:c r="D43" s="25" t="s"/>
       <x:c r="E43" s="25" t="s"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
       <x:c r="B44" s="24" t="s">
-        <x:v>150</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="25" t="s"/>
       <x:c r="D44" s="25" t="s"/>
       <x:c r="E44" s="25" t="s"/>
       <x:c r="F44" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
       <x:c r="B45" s="24" t="s">
-        <x:v>159</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C45" s="25" t="s"/>
       <x:c r="D45" s="25" t="s"/>
@@ -7035,7 +7078,7 @@
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="24" t="s">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C46" s="25" t="s"/>
       <x:c r="D46" s="25" t="s"/>
@@ -7046,29 +7089,29 @@
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C47" s="25" t="s"/>
       <x:c r="D47" s="25" t="s"/>
       <x:c r="E47" s="25" t="s"/>
       <x:c r="F47" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C48" s="25" t="s"/>
       <x:c r="D48" s="25" t="s"/>
       <x:c r="E48" s="25" t="s"/>
       <x:c r="F48" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C49" s="25" t="s"/>
       <x:c r="D49" s="25" t="s"/>
@@ -7079,28 +7122,48 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="24" t="s">
-        <x:v>229</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C50" s="25" t="s"/>
       <x:c r="D50" s="25" t="s"/>
       <x:c r="E50" s="25" t="s"/>
       <x:c r="F50" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C51" s="25" t="s"/>
+      <x:c r="D51" s="25" t="s"/>
+      <x:c r="E51" s="25" t="s"/>
+      <x:c r="F51" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B51" s="27" t="s">
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C53" s="28" t="s"/>
+      <x:c r="D53" s="28" t="s"/>
+      <x:c r="E53" s="28" t="s"/>
+      <x:c r="F53" s="29" t="n">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8042,13 +8105,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="18">
+  <x:mergeCells count="19">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B38:F38"/>
-    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B39:F39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
     <x:mergeCell ref="B42:E42"/>
@@ -8061,6 +8123,8 @@
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -486,6 +486,15 @@
     <x:t>GAISANO MALL BUTUAN, Imadejas, Butuan City (Capital), Agusan Del Norte</x:t>
   </x:si>
   <x:si>
+    <x:t>WDN-MM-00015-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1110-190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516334</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-MM-0017-21</x:t>
   </x:si>
   <x:si>
@@ -495,15 +504,6 @@
     <x:t>1516335</x:t>
   </x:si>
   <x:si>
-    <x:t>WDN-MM-00015-21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70-4-2026-1110-190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1516334</x:t>
-  </x:si>
-  <x:si>
     <x:t>Duplicate Copy</x:t>
   </x:si>
   <x:si>
@@ -522,6 +522,21 @@
     <x:t>1516356</x:t>
   </x:si>
   <x:si>
+    <x:t>RHITSY G. CONQUILLA JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urduja, Butuan City (Capital), Agusan Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIII-08478-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1121-627</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516359</x:t>
+  </x:si>
+  <x:si>
     <x:t>Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
@@ -730,6 +745,18 @@
   </x:si>
   <x:si>
     <x:t>1516330</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RHITSY GENON CONQUILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RLM-14-1608-XIII</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-4-2026-1122-258</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516360</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -6341,7 +6368,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46125.3770215625</x:v>
+        <x:v>46125.3805303819</x:v>
       </x:c>
       <x:c r="I19" s="32">
         <x:v>46140</x:v>
@@ -6350,10 +6377,10 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>4030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46125.4131163889</x:v>
+        <x:v>46125.4137300926</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6379,7 +6406,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46125.3805303819</x:v>
+        <x:v>46125.3770215625</x:v>
       </x:c>
       <x:c r="I20" s="32">
         <x:v>46140</x:v>
@@ -6388,10 +6415,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>1950</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46125.4137300926</x:v>
+        <x:v>46125.4131163889</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6435,35 +6462,35 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="D22" s="31" t="s"/>
       <x:c r="E22" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="G22" s="30" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46128.3211489699</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46128.3211489815</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46118.2457655324</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46118.2457900694</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>170</x:v>
-      </x:c>
       <x:c r="K22" s="33" t="n">
-        <x:v>1710</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46118.2697333565</x:v>
+        <x:v>46128.3498036806</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6471,7 +6498,7 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
         <x:v>171</x:v>
@@ -6487,19 +6514,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46125.1134160069</x:v>
+        <x:v>46118.2457655324</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46125.1134349537</x:v>
+        <x:v>46118.2457900694</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
         <x:v>175</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>1374</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46125.1559774537</x:v>
+        <x:v>46118.2697333565</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6507,37 +6534,35 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s">
+      <x:c r="D24" s="31" t="s"/>
+      <x:c r="E24" s="30" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E24" s="30" t="s">
+      <x:c r="F24" s="30" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="s">
+      <x:c r="G24" s="30" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="H24" s="32">
+        <x:v>46125.1134160069</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46125.1134349537</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46127.3855537963</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46127.3855756134</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>181</x:v>
-      </x:c>
       <x:c r="K24" s="33" t="n">
-        <x:v>7376</x:v>
+        <x:v>1374</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46127.4285094444</x:v>
+        <x:v>46125.1559774537</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6545,13 +6570,13 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="30" t="s">
-        <x:v>44</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s">
         <x:v>182</x:v>
       </x:c>
       <x:c r="D25" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E25" s="30" t="s">
         <x:v>183</x:v>
@@ -6563,19 +6588,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46125.0306295139</x:v>
+        <x:v>46127.3855537963</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46215</x:v>
+        <x:v>46127.3855756134</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
         <x:v>186</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>3006</x:v>
+        <x:v>7376</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46125.1001882292</x:v>
+        <x:v>46127.4285094444</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6583,13 +6608,13 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="30" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="30" t="s">
         <x:v>187</x:v>
       </x:c>
       <x:c r="D26" s="31" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="30" t="s">
         <x:v>188</x:v>
@@ -6601,19 +6626,19 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.1363557639</x:v>
+        <x:v>46125.0306295139</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.4024510301</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
         <x:v>191</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>3006</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.2066796875</x:v>
+        <x:v>46125.1001882292</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6639,10 +6664,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.1496079398</x:v>
+        <x:v>46119.1363557639</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.4042721991</x:v>
+        <x:v>46119.4024510301</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
         <x:v>196</x:v>
@@ -6651,7 +6676,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46120.1632395602</x:v>
+        <x:v>46120.2066796875</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6668,28 +6693,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E28" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.147375544</x:v>
+        <x:v>46119.1496079398</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.4211153819</x:v>
+        <x:v>46119.4042721991</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.1628406018</x:v>
+        <x:v>46120.1632395602</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6700,13 +6725,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D29" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
         <x:v>203</x:v>
@@ -6715,10 +6740,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.1392493403</x:v>
+        <x:v>46119.147375544</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.4026281134</x:v>
+        <x:v>46119.4211153819</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
         <x:v>205</x:v>
@@ -6727,7 +6752,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.1983392245</x:v>
+        <x:v>46120.1628406018</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6753,10 +6778,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.1552351505</x:v>
+        <x:v>46119.1392493403</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.4032803009</x:v>
+        <x:v>46119.4026281134</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
         <x:v>210</x:v>
@@ -6765,7 +6790,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.1647675232</x:v>
+        <x:v>46120.1983392245</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6791,10 +6816,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.1422446296</x:v>
+        <x:v>46119.1552351505</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.4022374537</x:v>
+        <x:v>46119.4032803009</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
         <x:v>215</x:v>
@@ -6803,7 +6828,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46120.207101169</x:v>
+        <x:v>46120.1647675232</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6829,10 +6854,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.1531599306</x:v>
+        <x:v>46119.1422446296</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.403984375</x:v>
+        <x:v>46119.4022374537</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
         <x:v>220</x:v>
@@ -6841,7 +6866,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46120.1636090856</x:v>
+        <x:v>46120.207101169</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6867,10 +6892,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.1574735532</x:v>
+        <x:v>46119.1531599306</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.403066169</x:v>
+        <x:v>46119.403984375</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
         <x:v>225</x:v>
@@ -6879,7 +6904,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46120.1653577778</x:v>
+        <x:v>46120.1636090856</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6896,28 +6921,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E34" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.1452747338</x:v>
+        <x:v>46119.1574735532</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.4028227894</x:v>
+        <x:v>46119.403066169</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46120.1874508102</x:v>
+        <x:v>46120.1653577778</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6925,16 +6950,16 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="30" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D35" s="31" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E35" s="30" t="s">
-        <x:v>231</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
         <x:v>232</x:v>
@@ -6943,10 +6968,10 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46125.1213370023</x:v>
+        <x:v>46119.1452747338</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46043</x:v>
+        <x:v>46119.4028227894</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
         <x:v>234</x:v>
@@ -6955,7 +6980,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46125.157450625</x:v>
+        <x:v>46120.1874508102</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6963,133 +6988,187 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="C36" s="30" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="D36" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F36" s="30" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F36" s="30" t="s">
+      <x:c r="G36" s="30" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="H36" s="32">
+        <x:v>46125.1213370023</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46043</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H36" s="32">
-        <x:v>46125.2289653241</x:v>
-      </x:c>
-      <x:c r="I36" s="32">
-        <x:v>46124</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="s">
+      <x:c r="K36" s="33" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="K36" s="33" t="n">
-        <x:v>3780</x:v>
-      </x:c>
       <x:c r="L36" s="34">
-        <x:v>46125.2566478009</x:v>
+        <x:v>46125.157450625</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="18" t="s">
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F37" s="30" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H37" s="32">
+        <x:v>46128.323707662</x:v>
+      </x:c>
+      <x:c r="I37" s="32">
+        <x:v>45052</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="K37" s="33" t="n">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="L37" s="34">
+        <x:v>46128.350051956</x:v>
+      </x:c>
+      <x:c r="M37" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C38" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E38" s="30" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F38" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>46125.2289653241</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46124</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="K38" s="33" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L38" s="34">
+        <x:v>46125.2566478009</x:v>
+      </x:c>
+      <x:c r="M38" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C39" s="19" t="s"/>
-      <x:c r="D39" s="19" t="s"/>
-      <x:c r="E39" s="20" t="s"/>
-      <x:c r="F39" s="20" t="s"/>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B40" s="21" t="s">
+      <x:c r="C41" s="19" t="s"/>
+      <x:c r="D41" s="19" t="s"/>
+      <x:c r="E41" s="20" t="s"/>
+      <x:c r="F41" s="20" t="s"/>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B42" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C40" s="22" t="s"/>
-      <x:c r="D40" s="22" t="s"/>
-      <x:c r="E40" s="22" t="s"/>
-      <x:c r="F40" s="23" t="s">
+      <x:c r="C42" s="22" t="s"/>
+      <x:c r="D42" s="22" t="s"/>
+      <x:c r="E42" s="22" t="s"/>
+      <x:c r="F42" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="24" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C41" s="25" t="s"/>
-      <x:c r="D41" s="25" t="s"/>
-      <x:c r="E41" s="25" t="s"/>
-      <x:c r="F41" s="26" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="24" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C42" s="25" t="s"/>
-      <x:c r="D42" s="25" t="s"/>
-      <x:c r="E42" s="25" t="s"/>
-      <x:c r="F42" s="26" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="18" customHeight="1">
       <x:c r="B43" s="24" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C43" s="25" t="s"/>
       <x:c r="D43" s="25" t="s"/>
       <x:c r="E43" s="25" t="s"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
       <x:c r="B44" s="24" t="s">
-        <x:v>26</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C44" s="25" t="s"/>
       <x:c r="D44" s="25" t="s"/>
       <x:c r="E44" s="25" t="s"/>
       <x:c r="F44" s="26" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
       <x:c r="B45" s="24" t="s">
-        <x:v>150</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C45" s="25" t="s"/>
       <x:c r="D45" s="25" t="s"/>
       <x:c r="E45" s="25" t="s"/>
       <x:c r="F45" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="24" t="s">
-        <x:v>159</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C46" s="25" t="s"/>
       <x:c r="D46" s="25" t="s"/>
       <x:c r="E46" s="25" t="s"/>
       <x:c r="F46" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="24" t="s">
-        <x:v>165</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C47" s="25" t="s"/>
       <x:c r="D47" s="25" t="s"/>
@@ -7100,40 +7179,40 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="24" t="s">
-        <x:v>176</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C48" s="25" t="s"/>
       <x:c r="D48" s="25" t="s"/>
       <x:c r="E48" s="25" t="s"/>
       <x:c r="F48" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="24" t="s">
-        <x:v>44</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C49" s="25" t="s"/>
       <x:c r="D49" s="25" t="s"/>
       <x:c r="E49" s="25" t="s"/>
       <x:c r="F49" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C50" s="25" t="s"/>
       <x:c r="D50" s="25" t="s"/>
       <x:c r="E50" s="25" t="s"/>
       <x:c r="F50" s="26" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C51" s="25" t="s"/>
       <x:c r="D51" s="25" t="s"/>
@@ -7144,28 +7223,48 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="24" t="s">
-        <x:v>235</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C52" s="25" t="s"/>
       <x:c r="D52" s="25" t="s"/>
       <x:c r="E52" s="25" t="s"/>
       <x:c r="F52" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="25" t="s"/>
+      <x:c r="D53" s="25" t="s"/>
+      <x:c r="E53" s="25" t="s"/>
+      <x:c r="F53" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="24" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C54" s="25" t="s"/>
+      <x:c r="D54" s="25" t="s"/>
+      <x:c r="E54" s="25" t="s"/>
+      <x:c r="F54" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B53" s="27" t="s">
+    <x:row r="55" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B55" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C53" s="28" t="s"/>
-      <x:c r="D53" s="28" t="s"/>
-      <x:c r="E53" s="28" t="s"/>
-      <x:c r="F53" s="29" t="n">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C55" s="28" t="s"/>
+      <x:c r="D55" s="28" t="s"/>
+      <x:c r="E55" s="28" t="s"/>
+      <x:c r="F55" s="29" t="n">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8110,9 +8209,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B39:F39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B41:F41"/>
     <x:mergeCell ref="B42:E42"/>
     <x:mergeCell ref="B43:E43"/>
     <x:mergeCell ref="B44:E44"/>
@@ -8125,6 +8222,8 @@
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-JAN-JOSEPH-JAMERO-evaluator-cache-serviceTracking-JAN-JOSEPH-JAMERO-XIII-202501-202612.xlsx
@@ -786,7 +786,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -826,14 +826,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1113,7 +1105,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1124,16 +1116,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1145,65 +1134,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1238,99 +1227,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1632,17 +1617,17 @@
       <x:c r="B5" s="12">
         <x:v>45717</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1665,80 +1650,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45743.3040092824</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45537</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45743.3122342361</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1758,44 +1743,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2901,17 +2886,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2934,173 +2919,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46030.2246127662</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46030.2246403009</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46030.2605660764</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46036.0630976157</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46036.0631306944</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46036.0820433218</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+      <x:c r="B12" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4205,17 +4190,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4238,537 +4223,537 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46111.1470208796</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46111.1470245139</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>97720</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46111.1717733681</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46111.3583193056</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46111.3723021991</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46100.1079781713</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46100.1417990741</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46100.1612414352</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46100.0888710764</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46100.1424897801</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46100.1669975463</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46100.1182232523</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>46100.1416081713</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46100.1503302546</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>46100.1012338657</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>46100.1420214352</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>46100.1632961806</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>46100.1284434491</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>46100.1411114583</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>46100.1586730671</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>46112.1495942824</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>46112.1682116435</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>46112.2080237037</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="C16" s="29" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H16" s="32">
+      <x:c r="H16" s="31">
         <x:v>46100.1227937384</x:v>
       </x:c>
-      <x:c r="I16" s="32">
+      <x:c r="I16" s="31">
         <x:v>46100.1413909606</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K16" s="33" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="34">
+      <x:c r="L16" s="33">
         <x:v>46100.1550834606</x:v>
       </x:c>
-      <x:c r="M16" s="30" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="30" t="s">
+      <x:c r="B17" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="C17" s="29" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H17" s="32">
+      <x:c r="H17" s="31">
         <x:v>46100.0935301273</x:v>
       </x:c>
-      <x:c r="I17" s="32">
+      <x:c r="I17" s="31">
         <x:v>46100.1422867824</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K17" s="33" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L17" s="34">
+      <x:c r="L17" s="33">
         <x:v>46100.1651693866</x:v>
       </x:c>
-      <x:c r="M17" s="30" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s">
+      <x:c r="C18" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="30" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H18" s="32">
+      <x:c r="H18" s="31">
         <x:v>46093.1010420255</x:v>
       </x:c>
-      <x:c r="I18" s="32">
+      <x:c r="I18" s="31">
         <x:v>45374</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="K18" s="33" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L18" s="34">
+      <x:c r="L18" s="33">
         <x:v>46093.1172837847</x:v>
       </x:c>
-      <x:c r="M18" s="30" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="18" t="s">
+      <x:c r="B21" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C21" s="19" t="s"/>
-      <x:c r="D21" s="19" t="s"/>
-      <x:c r="E21" s="20" t="s"/>
-      <x:c r="F21" s="20" t="s"/>
+      <x:c r="C21" s="18" t="s"/>
+      <x:c r="D21" s="18" t="s"/>
+      <x:c r="E21" s="19" t="s"/>
+      <x:c r="F21" s="19" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+      <x:c r="B22" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="s">
+      <x:c r="C22" s="21" t="s"/>
+      <x:c r="D22" s="21" t="s"/>
+      <x:c r="E22" s="21" t="s"/>
+      <x:c r="F22" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+      <x:c r="B23" s="23" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="C23" s="24" t="s"/>
+      <x:c r="D23" s="24" t="s"/>
+      <x:c r="E23" s="24" t="s"/>
+      <x:c r="F23" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="24" t="s">
+      <x:c r="B24" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="n">
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="24" t="s">
+      <x:c r="B25" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="n">
+      <x:c r="C25" s="24" t="s"/>
+      <x:c r="D25" s="24" t="s"/>
+      <x:c r="E25" s="24" t="s"/>
+      <x:c r="F25" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="24" t="s">
+      <x:c r="B26" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="n">
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="27" t="s">
+      <x:c r="B27" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -5864,17 +5849,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5897,1371 +5882,1371 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46127.1008034144</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46127.152407338</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46127.2663131018</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46127.1031398843</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46127.151645162</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46127.2649922801</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46127.0508113889</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46127.1521238079</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46127.2659745833</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s"/>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="D11" s="30" t="s"/>
+      <x:c r="E11" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46127.0960319676</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46127.1525701505</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46127.2673643403</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="D12" s="30" t="s"/>
+      <x:c r="E12" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46127.0942539931</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>46127.1508667708</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46127.2644301042</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s"/>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="D13" s="30" t="s"/>
+      <x:c r="E13" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>46127.0914937616</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>46127.1519132986</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>46127.2655630324</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>46118.0859375579</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>46150</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>46118.1095564468</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>46120.1844251157</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>46120.1844620486</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>46120.2675123495</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="C16" s="29" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H16" s="32">
+      <x:c r="H16" s="31">
         <x:v>46120.1809357755</x:v>
       </x:c>
-      <x:c r="I16" s="32">
+      <x:c r="I16" s="31">
         <x:v>46120.180990625</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="K16" s="33" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="34">
+      <x:c r="L16" s="33">
         <x:v>46120.2677879514</x:v>
       </x:c>
-      <x:c r="M16" s="30" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="30" t="s">
+      <x:c r="B17" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="C17" s="29" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H17" s="32">
+      <x:c r="H17" s="31">
         <x:v>46120.1772691204</x:v>
       </x:c>
-      <x:c r="I17" s="32">
+      <x:c r="I17" s="31">
         <x:v>46120.1774708102</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="K17" s="33" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L17" s="34">
+      <x:c r="L17" s="33">
         <x:v>46120.2680576968</x:v>
       </x:c>
-      <x:c r="M17" s="30" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s">
+      <x:c r="C18" s="29" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E18" s="30" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H18" s="32">
+      <x:c r="H18" s="31">
         <x:v>46120.1872445139</x:v>
       </x:c>
-      <x:c r="I18" s="32">
+      <x:c r="I18" s="31">
         <x:v>46120.1873116204</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="K18" s="33" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L18" s="34">
+      <x:c r="L18" s="33">
         <x:v>46120.2671879514</x:v>
       </x:c>
-      <x:c r="M18" s="30" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="30" t="s">
+      <x:c r="B19" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s">
+      <x:c r="C19" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D19" s="31" t="s">
+      <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="30" t="s">
+      <x:c r="E19" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F19" s="30" t="s">
+      <x:c r="F19" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="G19" s="29" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H19" s="32">
+      <x:c r="H19" s="31">
         <x:v>46125.3805303819</x:v>
       </x:c>
-      <x:c r="I19" s="32">
+      <x:c r="I19" s="31">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="J19" s="31" t="s">
+      <x:c r="J19" s="30" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="K19" s="33" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L19" s="34">
+      <x:c r="L19" s="33">
         <x:v>46125.4137300926</x:v>
       </x:c>
-      <x:c r="M19" s="30" t="s">
+      <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="30" t="s">
+      <x:c r="B20" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s">
+      <x:c r="C20" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D20" s="31" t="s">
+      <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="30" t="s">
+      <x:c r="E20" s="29" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F20" s="30" t="s">
+      <x:c r="F20" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="G20" s="29" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H20" s="32">
+      <x:c r="H20" s="31">
         <x:v>46125.3770215625</x:v>
       </x:c>
-      <x:c r="I20" s="32">
+      <x:c r="I20" s="31">
         <x:v>46140</x:v>
       </x:c>
-      <x:c r="J20" s="31" t="s">
+      <x:c r="J20" s="30" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="K20" s="33" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L20" s="34">
+      <x:c r="L20" s="33">
         <x:v>46125.4131163889</x:v>
       </x:c>
-      <x:c r="M20" s="30" t="s">
+      <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="30" t="s">
+      <x:c r="B21" s="29" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s">
+      <x:c r="C21" s="29" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="s"/>
-      <x:c r="E21" s="30" t="s">
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="s">
+      <x:c r="F21" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="G21" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H21" s="32">
+      <x:c r="H21" s="31">
         <x:v>46128.2754106944</x:v>
       </x:c>
-      <x:c r="I21" s="32">
+      <x:c r="I21" s="31">
         <x:v>46128.2754107639</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="s">
+      <x:c r="J21" s="30" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="K21" s="33" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>750</x:v>
       </x:c>
-      <x:c r="L21" s="34">
+      <x:c r="L21" s="33">
         <x:v>46128.2984009838</x:v>
       </x:c>
-      <x:c r="M21" s="30" t="s">
+      <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="30" t="s">
+      <x:c r="B22" s="29" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s">
+      <x:c r="C22" s="29" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="30" t="s">
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="F22" s="29" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="G22" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H22" s="32">
+      <x:c r="H22" s="31">
         <x:v>46128.3211489699</x:v>
       </x:c>
-      <x:c r="I22" s="32">
+      <x:c r="I22" s="31">
         <x:v>46128.3211489815</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="s">
+      <x:c r="J22" s="30" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="K22" s="33" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L22" s="34">
+      <x:c r="L22" s="33">
         <x:v>46128.3498036806</x:v>
       </x:c>
-      <x:c r="M22" s="30" t="s">
+      <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="30" t="s">
+      <x:c r="B23" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s">
+      <x:c r="C23" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="30" t="s">
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="s">
+      <x:c r="F23" s="29" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="G23" s="29" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H23" s="32">
+      <x:c r="H23" s="31">
         <x:v>46118.2457655324</x:v>
       </x:c>
-      <x:c r="I23" s="32">
+      <x:c r="I23" s="31">
         <x:v>46118.2457900694</x:v>
       </x:c>
-      <x:c r="J23" s="31" t="s">
+      <x:c r="J23" s="30" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="K23" s="33" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>1710</x:v>
       </x:c>
-      <x:c r="L23" s="34">
+      <x:c r="L23" s="33">
         <x:v>46118.2697333565</x:v>
       </x:c>
-      <x:c r="M23" s="30" t="s">
+      <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="30" t="s">
+      <x:c r="B24" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s">
+      <x:c r="C24" s="29" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="s"/>
-      <x:c r="E24" s="30" t="s">
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H24" s="32">
+      <x:c r="H24" s="31">
         <x:v>46125.1134160069</x:v>
       </x:c>
-      <x:c r="I24" s="32">
+      <x:c r="I24" s="31">
         <x:v>46125.1134349537</x:v>
       </x:c>
-      <x:c r="J24" s="31" t="s">
+      <x:c r="J24" s="30" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="K24" s="33" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>1374</x:v>
       </x:c>
-      <x:c r="L24" s="34">
+      <x:c r="L24" s="33">
         <x:v>46125.1559774537</x:v>
       </x:c>
-      <x:c r="M24" s="30" t="s">
+      <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+      <x:c r="B25" s="29" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="C25" s="30" t="s">
+      <x:c r="C25" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D25" s="31" t="s">
+      <x:c r="D25" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E25" s="30" t="s">
+      <x:c r="E25" s="29" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F25" s="30" t="s">
+      <x:c r="F25" s="29" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="G25" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H25" s="32">
+      <x:c r="H25" s="31">
         <x:v>46127.3855537963</x:v>
       </x:c>
-      <x:c r="I25" s="32">
+      <x:c r="I25" s="31">
         <x:v>46127.3855756134</x:v>
       </x:c>
-      <x:c r="J25" s="31" t="s">
+      <x:c r="J25" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K25" s="33" t="n">
+      <x:c r="K25" s="32" t="n">
         <x:v>7376</x:v>
       </x:c>
-      <x:c r="L25" s="34">
+      <x:c r="L25" s="33">
         <x:v>46127.4285094444</x:v>
       </x:c>
-      <x:c r="M25" s="30" t="s">
+      <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="30" t="s">
+      <x:c r="B26" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s">
+      <x:c r="C26" s="29" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="s">
+      <x:c r="D26" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E26" s="30" t="s">
+      <x:c r="E26" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F26" s="30" t="s">
+      <x:c r="F26" s="29" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="G26" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H26" s="32">
+      <x:c r="H26" s="31">
         <x:v>46125.0306295139</x:v>
       </x:c>
-      <x:c r="I26" s="32">
+      <x:c r="I26" s="31">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="J26" s="31" t="s">
+      <x:c r="J26" s="30" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K26" s="33" t="n">
+      <x:c r="K26" s="32" t="n">
         <x:v>3006</x:v>
       </x:c>
-      <x:c r="L26" s="34">
+      <x:c r="L26" s="33">
         <x:v>46125.1001882292</x:v>
       </x:c>
-      <x:c r="M26" s="30" t="s">
+      <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="30" t="s">
+      <x:c r="B27" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s">
+      <x:c r="C27" s="29" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D27" s="31" t="s">
+      <x:c r="D27" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E27" s="30" t="s">
+      <x:c r="E27" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F27" s="30" t="s">
+      <x:c r="F27" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="G27" s="29" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H27" s="32">
+      <x:c r="H27" s="31">
         <x:v>46119.1363557639</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="31">
         <x:v>46119.4024510301</x:v>
       </x:c>
-      <x:c r="J27" s="31" t="s">
+      <x:c r="J27" s="30" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K27" s="33" t="n">
+      <x:c r="K27" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L27" s="34">
+      <x:c r="L27" s="33">
         <x:v>46120.2066796875</x:v>
       </x:c>
-      <x:c r="M27" s="30" t="s">
+      <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="30" t="s">
+      <x:c r="B28" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C28" s="30" t="s">
+      <x:c r="C28" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D28" s="31" t="s">
+      <x:c r="D28" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E28" s="30" t="s">
+      <x:c r="E28" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F28" s="30" t="s">
+      <x:c r="F28" s="29" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="G28" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H28" s="32">
+      <x:c r="H28" s="31">
         <x:v>46119.1496079398</x:v>
       </x:c>
-      <x:c r="I28" s="32">
+      <x:c r="I28" s="31">
         <x:v>46119.4042721991</x:v>
       </x:c>
-      <x:c r="J28" s="31" t="s">
+      <x:c r="J28" s="30" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K28" s="33" t="n">
+      <x:c r="K28" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L28" s="34">
+      <x:c r="L28" s="33">
         <x:v>46120.1632395602</x:v>
       </x:c>
-      <x:c r="M28" s="30" t="s">
+      <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="30" t="s">
+      <x:c r="B29" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C29" s="30" t="s">
+      <x:c r="C29" s="29" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D29" s="31" t="s">
+      <x:c r="D29" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E29" s="30" t="s">
+      <x:c r="E29" s="29" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F29" s="30" t="s">
+      <x:c r="F29" s="29" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="G29" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="H29" s="32">
+      <x:c r="H29" s="31">
         <x:v>46119.147375544</x:v>
       </x:c>
-      <x:c r="I29" s="32">
+      <x:c r="I29" s="31">
         <x:v>46119.4211153819</x:v>
       </x:c>
-      <x:c r="J29" s="31" t="s">
+      <x:c r="J29" s="30" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="K29" s="33" t="n">
+      <x:c r="K29" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L29" s="34">
+      <x:c r="L29" s="33">
         <x:v>46120.1628406018</x:v>
       </x:c>
-      <x:c r="M29" s="30" t="s">
+      <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="30" t="s">
+      <x:c r="B30" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C30" s="30" t="s">
+      <x:c r="C30" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D30" s="31" t="s">
+      <x:c r="D30" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E30" s="30" t="s">
+      <x:c r="E30" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F30" s="30" t="s">
+      <x:c r="F30" s="29" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="G30" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H30" s="32">
+      <x:c r="H30" s="31">
         <x:v>46119.1392493403</x:v>
       </x:c>
-      <x:c r="I30" s="32">
+      <x:c r="I30" s="31">
         <x:v>46119.4026281134</x:v>
       </x:c>
-      <x:c r="J30" s="31" t="s">
+      <x:c r="J30" s="30" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="K30" s="33" t="n">
+      <x:c r="K30" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L30" s="34">
+      <x:c r="L30" s="33">
         <x:v>46120.1983392245</x:v>
       </x:c>
-      <x:c r="M30" s="30" t="s">
+      <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="30" t="s">
+      <x:c r="B31" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C31" s="30" t="s">
+      <x:c r="C31" s="29" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="D31" s="31" t="s">
+      <x:c r="D31" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E31" s="30" t="s">
+      <x:c r="E31" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="F31" s="30" t="s">
+      <x:c r="F31" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="G31" s="29" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="H31" s="32">
+      <x:c r="H31" s="31">
         <x:v>46119.1552351505</x:v>
       </x:c>
-      <x:c r="I31" s="32">
+      <x:c r="I31" s="31">
         <x:v>46119.4032803009</x:v>
       </x:c>
-      <x:c r="J31" s="31" t="s">
+      <x:c r="J31" s="30" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="K31" s="33" t="n">
+      <x:c r="K31" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L31" s="34">
+      <x:c r="L31" s="33">
         <x:v>46120.1647675232</x:v>
       </x:c>
-      <x:c r="M31" s="30" t="s">
+      <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="30" t="s">
+      <x:c r="B32" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C32" s="30" t="s">
+      <x:c r="C32" s="29" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D32" s="31" t="s">
+      <x:c r="D32" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E32" s="30" t="s">
+      <x:c r="E32" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="F32" s="30" t="s">
+      <x:c r="F32" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="G32" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H32" s="32">
+      <x:c r="H32" s="31">
         <x:v>46119.1422446296</x:v>
       </x:c>
-      <x:c r="I32" s="32">
+      <x:c r="I32" s="31">
         <x:v>46119.4022374537</x:v>
       </x:c>
-      <x:c r="J32" s="31" t="s">
+      <x:c r="J32" s="30" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K32" s="33" t="n">
+      <x:c r="K32" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L32" s="34">
+      <x:c r="L32" s="33">
         <x:v>46120.207101169</x:v>
       </x:c>
-      <x:c r="M32" s="30" t="s">
+      <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="30" t="s">
+      <x:c r="B33" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C33" s="30" t="s">
+      <x:c r="C33" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D33" s="31" t="s">
+      <x:c r="D33" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E33" s="30" t="s">
+      <x:c r="E33" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F33" s="30" t="s">
+      <x:c r="F33" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G33" s="30" t="s">
+      <x:c r="G33" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H33" s="32">
+      <x:c r="H33" s="31">
         <x:v>46119.1531599306</x:v>
       </x:c>
-      <x:c r="I33" s="32">
+      <x:c r="I33" s="31">
         <x:v>46119.403984375</x:v>
       </x:c>
-      <x:c r="J33" s="31" t="s">
+      <x:c r="J33" s="30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="K33" s="33" t="n">
+      <x:c r="K33" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L33" s="34">
+      <x:c r="L33" s="33">
         <x:v>46120.1636090856</x:v>
       </x:c>
-      <x:c r="M33" s="30" t="s">
+      <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="30" t="s">
+      <x:c r="B34" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C34" s="30" t="s">
+      <x:c r="C34" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="D34" s="31" t="s">
+      <x:c r="D34" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E34" s="30" t="s">
+      <x:c r="E34" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="F34" s="30" t="s">
+      <x:c r="F34" s="29" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
+      <x:c r="G34" s="29" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="H34" s="32">
+      <x:c r="H34" s="31">
         <x:v>46119.1574735532</x:v>
       </x:c>
-      <x:c r="I34" s="32">
+      <x:c r="I34" s="31">
         <x:v>46119.403066169</x:v>
       </x:c>
-      <x:c r="J34" s="31" t="s">
+      <x:c r="J34" s="30" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="K34" s="33" t="n">
+      <x:c r="K34" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L34" s="34">
+      <x:c r="L34" s="33">
         <x:v>46120.1653577778</x:v>
       </x:c>
-      <x:c r="M34" s="30" t="s">
+      <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="30" t="s">
+      <x:c r="B35" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="s">
+      <x:c r="C35" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D35" s="31" t="s">
+      <x:c r="D35" s="30" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E35" s="30" t="s">
+      <x:c r="E35" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F35" s="30" t="s">
+      <x:c r="F35" s="29" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
+      <x:c r="G35" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="H35" s="32">
+      <x:c r="H35" s="31">
         <x:v>46119.1452747338</x:v>
       </x:c>
-      <x:c r="I35" s="32">
+      <x:c r="I35" s="31">
         <x:v>46119.4028227894</x:v>
       </x:c>
-      <x:c r="J35" s="31" t="s">
+      <x:c r="J35" s="30" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="K35" s="33" t="n">
+      <x:c r="K35" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L35" s="34">
+      <x:c r="L35" s="33">
         <x:v>46120.1874508102</x:v>
       </x:c>
-      <x:c r="M35" s="30" t="s">
+      <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="30" t="s">
+      <x:c r="B36" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C36" s="30" t="s">
+      <x:c r="C36" s="29" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="D36" s="31" t="s">
+      <x:c r="D36" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E36" s="30" t="s">
+      <x:c r="E36" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="F36" s="30" t="s">
+      <x:c r="F36" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="G36" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="H36" s="32">
+      <x:c r="H36" s="31">
         <x:v>46125.1213370023</x:v>
       </x:c>
-      <x:c r="I36" s="32">
+      <x:c r="I36" s="31">
         <x:v>46043</x:v>
       </x:c>
-      <x:c r="J36" s="31" t="s">
+      <x:c r="J36" s="30" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="K36" s="33" t="n">
+      <x:c r="K36" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L36" s="34">
+      <x:c r="L36" s="33">
         <x:v>46125.157450625</x:v>
       </x:c>
-      <x:c r="M36" s="30" t="s">
+      <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="30" t="s">
+      <x:c r="B37" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C37" s="30" t="s">
+      <x:c r="C37" s="29" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D37" s="31" t="s">
+      <x:c r="D37" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E37" s="30" t="s">
+      <x:c r="E37" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="F37" s="30" t="s">
+      <x:c r="F37" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
+      <x:c r="G37" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H37" s="32">
+      <x:c r="H37" s="31">
         <x:v>46128.323707662</x:v>
       </x:c>
-      <x:c r="I37" s="32">
+      <x:c r="I37" s="31">
         <x:v>45052</x:v>
       </x:c>
-      <x:c r="J37" s="31" t="s">
+      <x:c r="J37" s="30" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="K37" s="33" t="n">
+      <x:c r="K37" s="32" t="n">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="L37" s="34">
+      <x:c r="L37" s="33">
         <x:v>46128.350051956</x:v>
       </x:c>
-      <x:c r="M37" s="30" t="s">
+      <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="30" t="s">
+      <x:c r="B38" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="C38" s="30" t="s">
+      <x:c r="C38" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="D38" s="31" t="s">
+      <x:c r="D38" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E38" s="30" t="s">
+      <x:c r="E38" s="29" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="F38" s="30" t="s">
+      <x:c r="F38" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="G38" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="H38" s="32">
+      <x:c r="H38" s="31">
         <x:v>46125.2289653241</x:v>
       </x:c>
-      <x:c r="I38" s="32">
+      <x:c r="I38" s="31">
         <x:v>46124</x:v>
       </x:c>
-      <x:c r="J38" s="31" t="s">
+      <x:c r="J38" s="30" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="K38" s="33" t="n">
+      <x:c r="K38" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L38" s="34">
+      <x:c r="L38" s="33">
         <x:v>46125.2566478009</x:v>
       </x:c>
-      <x:c r="M38" s="30" t="s">
+      <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="18" t="s">
+      <x:c r="B41" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C41" s="19" t="s"/>
-      <x:c r="D41" s="19" t="s"/>
-      <x:c r="E41" s="20" t="s"/>
-      <x:c r="F41" s="20" t="s"/>
+      <x:c r="C41" s="18" t="s"/>
+      <x:c r="D41" s="18" t="s"/>
+      <x:c r="E41" s="19" t="s"/>
+      <x:c r="F41" s="19" t="s"/>
     </x:row>
     <x:row r="42" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B42" s="21" t="s">
+      <x:c r="B42" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C42" s="22" t="s"/>
-      <x:c r="D42" s="22" t="s"/>
-      <x:c r="E42" s="22" t="s"/>
-      <x:c r="F42" s="23" t="s">
+      <x:c r="C42" s="21" t="s"/>
+      <x:c r="D42" s="21" t="s"/>
+      <x:c r="E42" s="21" t="s"/>
+      <x:c r="F42" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B43" s="24" t="s">
+      <x:c r="B43" s="23" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C43" s="25" t="s"/>
-      <x:c r="D43" s="25" t="s"/>
-      <x:c r="E43" s="25" t="s"/>
-      <x:c r="F43" s="26" t="n">
+      <x:c r="C43" s="24" t="s"/>
+      <x:c r="D43" s="24" t="s"/>
+      <x:c r="E43" s="24" t="s"/>
+      <x:c r="F43" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="24" t="s">
+      <x:c r="B44" s="23" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C44" s="25" t="s"/>
-      <x:c r="D44" s="25" t="s"/>
-      <x:c r="E44" s="25" t="s"/>
-      <x:c r="F44" s="26" t="n">
+      <x:c r="C44" s="24" t="s"/>
+      <x:c r="D44" s="24" t="s"/>
+      <x:c r="E44" s="24" t="s"/>
+      <x:c r="F44" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="24" t="s">
+      <x:c r="B45" s="23" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C45" s="25" t="s"/>
-      <x:c r="D45" s="25" t="s"/>
-      <x:c r="E45" s="25" t="s"/>
-      <x:c r="F45" s="26" t="n">
+      <x:c r="C45" s="24" t="s"/>
+      <x:c r="D45" s="24" t="s"/>
+      <x:c r="E45" s="24" t="s"/>
+      <x:c r="F45" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="24" t="s">
+      <x:c r="B46" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C46" s="25" t="s"/>
-      <x:c r="D46" s="25" t="s"/>
-      <x:c r="E46" s="25" t="s"/>
-      <x:c r="F46" s="26" t="n">
+      <x:c r="C46" s="24" t="s"/>
+      <x:c r="D46" s="24" t="s"/>
+      <x:c r="E46" s="24" t="s"/>
+      <x:c r="F46" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="24" t="s">
+      <x:c r="B47" s="23" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C47" s="25" t="s"/>
-      <x:c r="D47" s="25" t="s"/>
-      <x:c r="E47" s="25" t="s"/>
-      <x:c r="F47" s="26" t="n">
+      <x:c r="C47" s="24" t="s"/>
+      <x:c r="D47" s="24" t="s"/>
+      <x:c r="E47" s="24" t="s"/>
+      <x:c r="F47" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="24" t="s">
+      <x:c r="B48" s="23" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C48" s="25" t="s"/>
-      <x:c r="D48" s="25" t="s"/>
-      <x:c r="E48" s="25" t="s"/>
-      <x:c r="F48" s="26" t="n">
+      <x:c r="C48" s="24" t="s"/>
+      <x:c r="D48" s="24" t="s"/>
+      <x:c r="E48" s="24" t="s"/>
+      <x:c r="F48" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="24" t="s">
+      <x:c r="B49" s="23" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C49" s="25" t="s"/>
-      <x:c r="D49" s="25" t="s"/>
-      <x:c r="E49" s="25" t="s"/>
-      <x:c r="F49" s="26" t="n">
+      <x:c r="C49" s="24" t="s"/>
+      <x:c r="D49" s="24" t="s"/>
+      <x:c r="E49" s="24" t="s"/>
+      <x:c r="F49" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="24" t="s">
+      <x:c r="B50" s="23" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="C50" s="25" t="s"/>
-      <x:c r="D50" s="25" t="s"/>
-      <x:c r="E50" s="25" t="s"/>
-      <x:c r="F50" s="26" t="n">
+      <x:c r="C50" s="24" t="s"/>
+      <x:c r="D50" s="24" t="s"/>
+      <x:c r="E50" s="24" t="s"/>
+      <x:c r="F50" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="24" t="s">
+      <x:c r="B51" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C51" s="25" t="s"/>
-      <x:c r="D51" s="25" t="s"/>
-      <x:c r="E51" s="25" t="s"/>
-      <x:c r="F51" s="26" t="n">
+      <x:c r="C51" s="24" t="s"/>
+      <x:c r="D51" s="24" t="s"/>
+      <x:c r="E51" s="24" t="s"/>
+      <x:c r="F51" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="24" t="s">
+      <x:c r="B52" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C52" s="25" t="s"/>
-      <x:c r="D52" s="25" t="s"/>
-      <x:c r="E52" s="25" t="s"/>
-      <x:c r="F52" s="26" t="n">
+      <x:c r="C52" s="24" t="s"/>
+      <x:c r="D52" s="24" t="s"/>
+      <x:c r="E52" s="24" t="s"/>
+      <x:c r="F52" s="25" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="24" t="s">
+      <x:c r="B53" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C53" s="25" t="s"/>
-      <x:c r="D53" s="25" t="s"/>
-      <x:c r="E53" s="25" t="s"/>
-      <x:c r="F53" s="26" t="n">
+      <x:c r="C53" s="24" t="s"/>
+      <x:c r="D53" s="24" t="s"/>
+      <x:c r="E53" s="24" t="s"/>
+      <x:c r="F53" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="24" t="s">
+      <x:c r="B54" s="23" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="C54" s="25" t="s"/>
-      <x:c r="D54" s="25" t="s"/>
-      <x:c r="E54" s="25" t="s"/>
-      <x:c r="F54" s="26" t="n">
+      <x:c r="C54" s="24" t="s"/>
+      <x:c r="D54" s="24" t="s"/>
+      <x:c r="E54" s="24" t="s"/>
+      <x:c r="F54" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B55" s="27" t="s">
+      <x:c r="B55" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C55" s="28" t="s"/>
-      <x:c r="D55" s="28" t="s"/>
-      <x:c r="E55" s="28" t="s"/>
-      <x:c r="F55" s="29" t="n">
+      <x:c r="C55" s="27" t="s"/>
+      <x:c r="D55" s="27" t="s"/>
+      <x:c r="E55" s="27" t="s"/>
+      <x:c r="F55" s="28" t="n">
         <x:v>31</x:v>
       </x:c>
     </x:row>
